--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0</v>
+        <v>673.6900000000001</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>0 de 24</t>
+          <t>1 de 24</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>673.6900000000001</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>50186.45</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0</v>
+        <v>673.6900000000001</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,11 +443,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BARRAGAN PUENTE NATALY CAROLINA</t>
+          <t>ARCOS GOMEZ CONSTRUCCIONES CIA. LTDA.</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BECERRA FARIAS ROSA DAYANA</t>
+          <t>BARRAGAN PUENTE NATALY CAROLINA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BELTRAN ESPINOZA SONIA SARITA</t>
+          <t>BECERRA FARIAS ROSA DAYANA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
+          <t>BELTRAN ESPINOZA SONIA SARITA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CERAMICAS AL COSTO S.A.S.</t>
+          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -866,7 +866,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CERAMICCENTER CIA. LTDA.</t>
+          <t>CERAMICAS AL COSTO S.A.S.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
+          <t>CERAMICCENTER CIA. LTDA.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONZA VEGA FRANCO BLADYMIR</t>
+          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CULMA OVIEDO NINI JOHANA</t>
+          <t>CONZA VEGA FRANCO BLADYMIR</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DDH S.A.S.</t>
+          <t>CULMA OVIEDO NINI JOHANA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>673.6900000000001</v>
+        <v>0</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F.V - AREA ANDINA S.A.</t>
+          <t>DDH S.A.S.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>761.8200000000001</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FERRIACABADOS MACONSE</t>
+          <t>F.V - AREA ANDINA S.A.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
+          <t>FERRIACABADOS MACONSE</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1946,137 +1946,197 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>1 de 24</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
-        </is>
-      </c>
-      <c r="R26" s="4" t="inlineStr">
-        <is>
-          <t>0 de 24</t>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
         </is>
       </c>
     </row>
@@ -2091,11 +2151,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2148,7 +2208,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BARRAGAN PUENTE NATALY CAROLINA</t>
+          <t>ARCOS GOMEZ CONSTRUCCIONES CIA. LTDA.</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -2175,7 +2235,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BECERRA FARIAS ROSA DAYANA</t>
+          <t>BARRAGAN PUENTE NATALY CAROLINA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -2191,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2202,14 +2262,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BELTRAN ESPINOZA SONIA SARITA</t>
+          <t>BECERRA FARIAS ROSA DAYANA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2548.88</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1653.75</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -2229,14 +2289,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
+          <t>BELTRAN ESPINOZA SONIA SARITA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1362.43</v>
+        <v>2548.88</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1653.75</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -2256,23 +2316,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CERAMICAS AL COSTO S.A.S.</t>
+          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>1362.43</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>24929.52</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10645.56</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -2283,23 +2343,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CERAMICCENTER CIA. LTDA.</t>
+          <t>CERAMICAS AL COSTO S.A.S.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>24929.52</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>10645.56</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="8">
@@ -2310,11 +2370,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
+          <t>CERAMICCENTER CIA. LTDA.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>663.55</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
@@ -2337,11 +2397,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONZA VEGA FRANCO BLADYMIR</t>
+          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>663.55</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
@@ -2353,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2364,11 +2424,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CULMA OVIEDO NINI JOHANA</t>
+          <t>CONZA VEGA FRANCO BLADYMIR</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4220.84</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
@@ -2380,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11">
@@ -2391,11 +2451,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DDH S.A.S.</t>
+          <t>CULMA OVIEDO NINI JOHANA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>4220.84</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
@@ -2404,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>673.6900000000001</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2418,23 +2478,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F.V - AREA ANDINA S.A.</t>
+          <t>DDH S.A.S.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6935.82</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5890.54</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>18531.43</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>761.8200000000001</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>12870</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2445,23 +2505,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FERRIACABADOS MACONSE</t>
+          <t>F.V - AREA ANDINA S.A.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>6935.82</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>5890.54</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>18531.43</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1000</v>
+        <v>12870</v>
       </c>
     </row>
     <row r="14">
@@ -2472,17 +2532,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
+          <t>FERRIACABADOS MACONSE</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3080.12</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>793.76</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -2499,23 +2559,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>3080.12</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>793.76</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
@@ -2526,7 +2586,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -2542,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2553,11 +2613,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3162.93</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -2569,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
@@ -2580,11 +2640,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>3162.93</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -2607,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -2634,7 +2694,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2661,11 +2721,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1687.32</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
@@ -2677,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2688,23 +2748,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>14679.01</v>
+        <v>1687.32</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5686.14</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3757.05</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="23">
@@ -2715,23 +2775,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>14679.01</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>5686.14</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>3757.05</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24">
@@ -2742,7 +2802,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -2769,39 +2829,66 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C26" s="2" t="n">
         <v>6348.54</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D26" s="2" t="n">
         <v>23307.46</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E26" s="2" t="n">
         <v>16458.65</v>
       </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="n">
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="26">
-      <c r="C26" s="6" t="n">
+    <row r="27">
+      <c r="C27" s="6" t="n">
         <v>41609.32</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D27" s="6" t="n">
         <v>64547.53</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E27" s="6" t="n">
         <v>50186.45</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>673.6900000000001</v>
-      </c>
-      <c r="G26" s="6" t="n">
+      <c r="F27" s="6" t="n">
+        <v>761.8200000000001</v>
+      </c>
+      <c r="G27" s="6" t="n">
         <v>38870</v>
       </c>
     </row>
@@ -2816,15 +2903,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2871,13 +2958,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>129.6</v>
+        <v>136.08</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>129.6</v>
+        <v>136.08</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -2895,13 +2982,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2344.03</v>
+        <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2344.03</v>
+        <v>3800</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -2919,13 +3006,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>207.39</v>
+        <v>241.5</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>207.39</v>
+        <v>241.5</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -2943,13 +3030,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>86.41</v>
+        <v>172.82</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>86.41</v>
+        <v>172.82</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -2967,13 +3054,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>855.91</v>
+        <v>560</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>855.91</v>
+        <v>560</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -2991,13 +3078,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>383</v>
+        <v>263.55</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>383</v>
+        <v>263.55</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -3015,13 +3102,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>415</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>415</v>
+        <v>250</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3063,13 +3150,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>388.107983534392</v>
+        <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>388.107983534392</v>
+        <v>203.763</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -3087,16 +3174,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>902.88</v>
+        <v>254</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>739.0700000000001</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>163.8099999999999</v>
+        <v>254</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8185694665957824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3111,16 +3198,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>34701</v>
+        <v>32148</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>58122.32</v>
+        <v>761.8200000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-23421.32</v>
+        <v>31386.18</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.674946543327282</v>
+        <v>0.02369727510265024</v>
       </c>
     </row>
     <row r="13">
@@ -3135,35 +3222,59 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>364.412605947529</v>
+        <v>327.6</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>364.412605947529</v>
+        <v>327.6</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAL SOLUBLE</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>40777.74058948192</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>58861.39</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-18083.64941051808</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1.443468646106953</v>
+      <c r="C15" s="2" t="n">
+        <v>38717.313</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>761.8200000000001</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>37955.49299999999</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.01967646876734447</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2903,7 +2903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3170,17 +3170,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>254</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>254</v>
+        <v>115</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -3194,20 +3194,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>32148</v>
+        <v>254</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>761.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>31386.18</v>
+        <v>254</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.02369727510265024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3218,20 +3218,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>327.6</v>
+        <v>32148</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>761.8200000000001</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>327.6</v>
+        <v>31386.18</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.02369727510265024</v>
       </c>
     </row>
     <row r="14">
@@ -3242,39 +3242,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>PUERTAS DE SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>SAL SOLUBLE</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n">
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>38717.313</v>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="C16" s="2" t="n">
+        <v>38832.313</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>761.8200000000001</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>37955.49299999999</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.01967646876734447</v>
+      <c r="E16" s="2" t="n">
+        <v>38070.49299999999</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.01961819786526752</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>388.8</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>3815.51</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>1373.76</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
+        <v>3062.45</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2061,57 +2061,57 @@
     <row r="27">
       <c r="C27" s="4" t="inlineStr">
         <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>3 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2788,7 +2788,7 @@
         <v>3757.05</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>4204.31</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2869,7 +2869,7 @@
         <v>16458.65</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>4436.21</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>15000</v>
@@ -2886,7 +2886,7 @@
         <v>50186.45</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>761.8200000000001</v>
+        <v>9402.34</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,9 +2909,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2961,13 +2961,13 @@
         <v>136.08</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>388.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>136.08</v>
+        <v>-252.72</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>2.857142857142857</v>
       </c>
     </row>
     <row r="3">
@@ -2985,13 +2985,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1373.76</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3800</v>
+        <v>2426.24</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>0.3615157894736842</v>
       </c>
     </row>
     <row r="4">
@@ -3225,13 +3225,13 @@
         <v>32148</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>761.8200000000001</v>
+        <v>7639.78</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>31386.18</v>
+        <v>24508.22</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.02369727510265024</v>
+        <v>0.2376440214010203</v>
       </c>
     </row>
     <row r="14">
@@ -3292,13 +3292,13 @@
         <v>38832.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>761.8200000000001</v>
+        <v>9402.34</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>38070.49299999999</v>
+        <v>29429.973</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.01961819786526752</v>
+        <v>0.2421267051488795</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>761.8200000000001</v>
+        <v>767.9400000000001</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -2491,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>761.8200000000001</v>
+        <v>767.9400000000001</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>50186.45</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>9402.34</v>
+        <v>9408.460000000001</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3225,13 +3225,13 @@
         <v>32148</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7639.78</v>
+        <v>7658.14</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24508.22</v>
+        <v>24489.86</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.2376440214010203</v>
+        <v>0.2382151300236407</v>
       </c>
     </row>
     <row r="14">
@@ -3292,13 +3292,13 @@
         <v>38832.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9402.34</v>
+        <v>9420.700000000001</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>29429.973</v>
+        <v>29411.613</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2421267051488795</v>
+        <v>0.2425995072711739</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>760.3200000000001</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
         <v>10645.56</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>760.3200000000001</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2500</v>
@@ -2788,7 +2788,7 @@
         <v>3757.05</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>4204.31</v>
+        <v>4115.1</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2886,7 +2886,7 @@
         <v>50186.45</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>9408.460000000001</v>
+        <v>10079.57</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2911,7 +2911,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2985,13 +2985,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1373.76</v>
+        <v>2134.08</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2426.24</v>
+        <v>1665.92</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3615157894736842</v>
+        <v>0.5616</v>
       </c>
     </row>
     <row r="4">
@@ -3177,13 +3177,13 @@
         <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>-89.20999999999999</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115</v>
+        <v>204.21</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-0.7757391304347826</v>
       </c>
     </row>
     <row r="12">
@@ -3292,13 +3292,13 @@
         <v>38832.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9420.700000000001</v>
+        <v>10091.81</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>29411.613</v>
+        <v>28740.503</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2425995072711739</v>
+        <v>0.259881763932012</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2788,7 +2788,7 @@
         <v>3757.05</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>4115.1</v>
+        <v>4048.19</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2886,7 +2886,7 @@
         <v>50186.45</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>10079.57</v>
+        <v>10012.66</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2911,7 +2911,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3177,13 +3177,13 @@
         <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-89.20999999999999</v>
+        <v>-156.12</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>204.21</v>
+        <v>271.12</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.7757391304347826</v>
+        <v>-1.357565217391304</v>
       </c>
     </row>
     <row r="12">
@@ -3292,13 +3292,13 @@
         <v>38832.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10091.81</v>
+        <v>10024.9</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>28740.503</v>
+        <v>28807.413</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.259881763932012</v>
+        <v>0.2581587143675939</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>760.3200000000001</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>767.9400000000001</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>388.8</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3815.51</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1373.76</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3062.45</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
     <row r="27">
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>3 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2156,9 +2156,9 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2176,22 +2176,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2548.88</v>
+        <v>1653.75</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1653.75</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1362.43</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
@@ -2347,16 +2347,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>24929.52</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>24929.52</v>
+        <v>10645.56</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>10645.56</v>
+        <v>760.3200000000001</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>760.3200000000001</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2500</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>663.55</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4220.84</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
@@ -2488,10 +2488,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>767.9400000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>767.9400000000001</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -2509,13 +2509,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6935.82</v>
+        <v>5890.54</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5890.54</v>
+        <v>18531.43</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18531.43</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>3080.12</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3080.12</v>
+        <v>793.76</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>793.76</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3162.93</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1687.32</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>14679.01</v>
+        <v>5686.14</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>5686.14</v>
+        <v>3757.05</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>3757.05</v>
+        <v>4048.19</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>4048.19</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2860,16 +2860,16 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6348.54</v>
+        <v>23307.46</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>23307.46</v>
+        <v>16458.65</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>16458.65</v>
+        <v>4436.21</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>4436.21</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>15000</v>
@@ -2877,16 +2877,16 @@
     </row>
     <row r="27">
       <c r="C27" s="6" t="n">
-        <v>41609.32</v>
+        <v>64547.53</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>64547.53</v>
+        <v>50186.45</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>50186.45</v>
+        <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>10012.66</v>
+        <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>915.84</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
+        <v>4460.68</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0</v>
@@ -2066,52 +2066,52 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>1 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>5376.52</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>1500</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0</v>
+        <v>5376.52</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2961,13 +2961,13 @@
         <v>136.08</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>388.8</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-252.72</v>
+        <v>136.08</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.857142857142857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2985,13 +2985,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2134.08</v>
+        <v>915.84</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1665.92</v>
+        <v>2884.16</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5616</v>
+        <v>0.2410105263157895</v>
       </c>
     </row>
     <row r="4">
@@ -3177,13 +3177,13 @@
         <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-156.12</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>271.12</v>
+        <v>115</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.357565217391304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3222,16 +3222,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32148</v>
+        <v>39250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7658.14</v>
+        <v>4460.68</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24489.86</v>
+        <v>34789.32</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.2382151300236407</v>
+        <v>0.113647898089172</v>
       </c>
     </row>
     <row r="14">
@@ -3289,16 +3289,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>38832.313</v>
+        <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10024.9</v>
+        <v>5376.52</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>28807.413</v>
+        <v>40557.793</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2581587143675939</v>
+        <v>0.1170480115812334</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>337.8</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>337.8</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>5376.52</v>
+        <v>5714.320000000001</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3225,13 +3225,13 @@
         <v>39250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4460.68</v>
+        <v>4798.48</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>34789.32</v>
+        <v>34451.52</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.113647898089172</v>
+        <v>0.1222542675159236</v>
       </c>
     </row>
     <row r="14">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5376.52</v>
+        <v>5714.32</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>40557.793</v>
+        <v>40219.99299999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1170480115812334</v>
+        <v>0.1244019911650796</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>462.67</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>3 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2491,7 +2491,7 @@
         <v>767.9400000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>462.67</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>5714.320000000001</v>
+        <v>6176.990000000001</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3225,13 +3225,13 @@
         <v>39250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4798.48</v>
+        <v>5261.15</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>34451.52</v>
+        <v>33988.85</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1222542675159236</v>
+        <v>0.1340420382165605</v>
       </c>
     </row>
     <row r="14">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5714.32</v>
+        <v>6176.99</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>40219.99299999999</v>
+        <v>39757.323</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1244019911650796</v>
+        <v>0.1344744178496803</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>89.56</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>1 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
         <v>760.3200000000001</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>89.56</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2500</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>6176.990000000001</v>
+        <v>6266.55</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3201,13 +3201,13 @@
         <v>254</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>89.56</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>254</v>
+        <v>164.44</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.3525984251968504</v>
       </c>
     </row>
     <row r="13">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6176.99</v>
+        <v>6266.549999999999</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39757.323</v>
+        <v>39667.763</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1344744178496803</v>
+        <v>0.1364241585587663</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>7858.37</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>3 de 25</t>
+          <t>4 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>7858.37</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>12870</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>6266.55</v>
+        <v>14124.92</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,7 +2909,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3225,13 +3225,13 @@
         <v>39250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5261.15</v>
+        <v>13119.52</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>33988.85</v>
+        <v>26130.48</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1340420382165605</v>
+        <v>0.3342552866242038</v>
       </c>
     </row>
     <row r="14">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6266.549999999999</v>
+        <v>14124.92</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>39667.763</v>
+        <v>31809.393</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1364241585587663</v>
+        <v>0.3075025852677932</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>462.67</v>
+        <v>484.7</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -2491,7 +2491,7 @@
         <v>767.9400000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>462.67</v>
+        <v>484.7</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>14124.92</v>
+        <v>14146.95</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3225,13 +3225,13 @@
         <v>39250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13119.52</v>
+        <v>13141.55</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26130.48</v>
+        <v>26108.45</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3342552866242038</v>
+        <v>0.3348165605095541</v>
       </c>
     </row>
     <row r="14">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>14124.92</v>
+        <v>14146.95</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>31809.393</v>
+        <v>31787.363</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3075025852677932</v>
+        <v>0.3079821831666449</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>732.67</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>732.67</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>14146.95</v>
+        <v>14879.62</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2985,13 +2985,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>915.84</v>
+        <v>1648.51</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2884.16</v>
+        <v>2151.49</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2410105263157895</v>
+        <v>0.4338184210526316</v>
       </c>
     </row>
     <row r="4">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>14146.95</v>
+        <v>14879.62</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>31787.363</v>
+        <v>31054.693</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3079821831666449</v>
+        <v>0.3239325686660427</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7858.37</v>
+        <v>15756.68</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7858.37</v>
+        <v>15756.68</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>12870</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>14879.62</v>
+        <v>22777.93</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3225,13 +3225,13 @@
         <v>39250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13141.55</v>
+        <v>21039.86</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26108.45</v>
+        <v>18210.14</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3348165605095541</v>
+        <v>0.5360473885350319</v>
       </c>
     </row>
     <row r="14">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>14879.62</v>
+        <v>22777.93</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>31054.693</v>
+        <v>23156.383</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3239325686660427</v>
+        <v>0.4958804978753029</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>4 de 25</t>
+          <t>5 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2869,7 +2869,7 @@
         <v>4436.21</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>15000</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>22777.93</v>
+        <v>22783.33</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3225,13 +3225,13 @@
         <v>39250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>21039.86</v>
+        <v>21045.26</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18210.14</v>
+        <v>18204.74</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.5360473885350319</v>
+        <v>0.5361849681528662</v>
       </c>
     </row>
     <row r="14">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>22777.93</v>
+        <v>22783.33</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>23156.383</v>
+        <v>23150.983</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4958804978753029</v>
+        <v>0.4959980570515988</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>-142.56</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>4048.19</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>-142.56</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>22783.33</v>
+        <v>22640.77</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2911,7 +2911,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3201,13 +3201,13 @@
         <v>254</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>89.56</v>
+        <v>-53</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>164.44</v>
+        <v>307</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.3525984251968504</v>
+        <v>-0.2086614173228346</v>
       </c>
     </row>
     <row r="13">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>22783.33</v>
+        <v>22640.77</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>23150.983</v>
+        <v>23293.543</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4959980570515988</v>
+        <v>0.4928944947973859</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -900,7 +900,7 @@
         <v>89.56</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>51.97</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>732.67</v>
+        <v>915.84</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
+        <v>764.72</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>268.4</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5.4</v>
+        <v>23543.77</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2086,24 +2086,24 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
           <t>1 de 25</t>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>5 de 25</t>
+          <t>6 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
         <v>760.3200000000001</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>89.56</v>
+        <v>141.53</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2500</v>
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>732.67</v>
+        <v>915.84</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>1033.12</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1000</v>
@@ -2869,7 +2869,7 @@
         <v>4436.21</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>5.4</v>
+        <v>23543.77</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>15000</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>22640.77</v>
+        <v>47447.4</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,8 +2909,8 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2985,13 +2985,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1648.51</v>
+        <v>1831.68</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2151.49</v>
+        <v>1968.32</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4338184210526316</v>
+        <v>0.482021052631579</v>
       </c>
     </row>
     <row r="4">
@@ -3057,13 +3057,13 @@
         <v>560</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>764.72</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>560</v>
+        <v>-204.72</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1.365571428571429</v>
       </c>
     </row>
     <row r="7">
@@ -3081,13 +3081,13 @@
         <v>263.55</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>268.4</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>263.55</v>
+        <v>-4.849999999999966</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1.018402580155568</v>
       </c>
     </row>
     <row r="8">
@@ -3225,13 +3225,13 @@
         <v>39250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>21045.26</v>
+        <v>44635.6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18204.74</v>
+        <v>-5385.599999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.5361849681528662</v>
+        <v>1.137212738853503</v>
       </c>
     </row>
     <row r="14">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>22640.77</v>
+        <v>47447.4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>23293.543</v>
+        <v>-1513.086999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4928944947973859</v>
+        <v>1.032940233589648</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>915.84</v>
+        <v>3205.44</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>313.21</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>915.84</v>
+        <v>3518.65</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>10012.66</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>47447.4</v>
+        <v>50050.21</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2911,7 +2911,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2985,13 +2985,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1831.68</v>
+        <v>4121.28</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1968.32</v>
+        <v>-321.2799999999997</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.482021052631579</v>
+        <v>1.084547368421052</v>
       </c>
     </row>
     <row r="4">
@@ -3201,13 +3201,13 @@
         <v>254</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-53</v>
+        <v>260.21</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>307</v>
+        <v>-6.20999999999998</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.2086614173228346</v>
+        <v>1.024448818897638</v>
       </c>
     </row>
     <row r="13">
@@ -3292,13 +3292,13 @@
         <v>45934.313</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>47447.4</v>
+        <v>50050.21</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-1513.086999999999</v>
+        <v>-4115.896999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.032940233589648</v>
+        <v>1.08960397426647</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>337.8</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -897,10 +897,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>89.56</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>51.97</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>915.84</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4460.68</v>
+        <v>0</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0</v>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3205.44</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>313.21</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>484.7</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>15756.68</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>764.72</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>268.4</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>-142.56</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>23543.77</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>6 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2157,9 +2157,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2176,22 +2176,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2218,10 +2218,10 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>337.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>337.8</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1653.75</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -2347,16 +2347,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>24929.52</v>
+        <v>10645.56</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10645.56</v>
+        <v>760.3200000000001</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>760.3200000000001</v>
+        <v>141.53</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>141.53</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2500</v>
@@ -2434,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>5376.52</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5376.52</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>1500</v>
@@ -2461,10 +2461,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>3518.65</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3518.65</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2485,13 +2485,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>767.9400000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>767.9400000000001</v>
+        <v>484.7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>484.7</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -2509,16 +2509,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5890.54</v>
+        <v>18531.43</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>18531.43</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>15756.68</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>15756.68</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>12870</v>
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3080.12</v>
+        <v>793.76</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>793.76</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>1033.12</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1033.12</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1000</v>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5686.14</v>
+        <v>3757.05</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3757.05</v>
+        <v>4048.19</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>4048.19</v>
+        <v>-142.56</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-142.56</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2860,16 +2860,16 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>23307.46</v>
+        <v>16458.65</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>16458.65</v>
+        <v>4436.21</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>4436.21</v>
+        <v>23543.77</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>23543.77</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>15000</v>
@@ -2877,16 +2877,16 @@
     </row>
     <row r="27">
       <c r="C27" s="6" t="n">
-        <v>64547.53</v>
+        <v>50186.45</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>50186.45</v>
+        <v>10012.66</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>10012.66</v>
+        <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>50050.21</v>
+        <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2151,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2160,7 +2160,6 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2194,11 +2193,6 @@
           <t>marzo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>PRESUPUESTO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2223,9 +2217,6 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2250,9 +2241,6 @@
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2277,9 +2265,6 @@
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2304,9 +2289,6 @@
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2331,9 +2313,6 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2358,9 +2337,6 @@
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>2500</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2385,9 +2361,6 @@
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2412,9 +2385,6 @@
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2439,9 +2409,6 @@
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>1500</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2466,9 +2433,6 @@
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2493,9 +2457,6 @@
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2520,9 +2481,6 @@
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>12870</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2547,9 +2505,6 @@
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2574,9 +2529,6 @@
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2601,9 +2553,6 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2628,9 +2577,6 @@
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>500</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2655,9 +2601,6 @@
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2682,9 +2625,6 @@
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2709,9 +2649,6 @@
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2736,9 +2673,6 @@
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2763,9 +2697,6 @@
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>500</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2790,9 +2721,6 @@
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2817,9 +2745,6 @@
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2844,9 +2769,6 @@
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2870,9 +2792,6 @@
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>15000</v>
       </c>
     </row>
     <row r="27">
@@ -2887,9 +2806,6 @@
       </c>
       <c r="F27" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>38870</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2151,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2160,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2193,6 +2194,11 @@
           <t>marzo</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2217,6 +2223,9 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2241,6 +2250,9 @@
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2265,6 +2277,9 @@
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2289,6 +2304,9 @@
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2313,6 +2331,9 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2337,6 +2358,9 @@
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>2500</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2361,6 +2385,9 @@
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2385,6 +2412,9 @@
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2409,6 +2439,9 @@
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2433,6 +2466,9 @@
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2457,6 +2493,9 @@
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2481,6 +2520,9 @@
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>12870</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2505,6 +2547,9 @@
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2529,6 +2574,9 @@
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2553,6 +2601,9 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2577,6 +2628,9 @@
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2601,6 +2655,9 @@
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2625,6 +2682,9 @@
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2649,6 +2709,9 @@
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2673,6 +2736,9 @@
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2697,6 +2763,9 @@
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2721,6 +2790,9 @@
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2745,6 +2817,9 @@
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2769,6 +2844,9 @@
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2792,6 +2870,9 @@
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="27">
@@ -2806,6 +2887,9 @@
       </c>
       <c r="F27" s="6" t="n">
         <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>38870</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>325.63</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>1 de 25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2788,7 +2788,7 @@
         <v>-142.56</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>325.63</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2886,7 +2886,7 @@
         <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0</v>
+        <v>325.63</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2903,15 +2903,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2985,13 +2985,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4121.28</v>
+        <v>325.63</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-321.2799999999997</v>
+        <v>3474.37</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.084547368421052</v>
+        <v>0.08569210526315789</v>
       </c>
     </row>
     <row r="4">
@@ -3006,13 +3006,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>241.5</v>
+        <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>241.5</v>
+        <v>199.5</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -3054,16 +3054,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>560</v>
+        <v>240</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>764.72</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-204.72</v>
+        <v>240</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.365571428571429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3081,13 +3081,13 @@
         <v>263.55</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>268.4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-4.849999999999966</v>
+        <v>263.55</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.018402580155568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3201,13 +3201,13 @@
         <v>254</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>260.21</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-6.20999999999998</v>
+        <v>254</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.024448818897638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3222,16 +3222,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>39250</v>
+        <v>68268</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>44635.6</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-5385.599999999999</v>
+        <v>68268</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.137212738853503</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3259,46 +3259,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SAL SOLUBLE</t>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>360</v>
+        <v>74230.31300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>325.63</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>360</v>
+        <v>73904.683</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>45934.313</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>50050.21</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>-4115.896999999999</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>1.08960397426647</v>
+        <v>0.004386752350081024</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0</v>
+        <v>396.6</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>396.58</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -2111,22 +2111,22 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>1 de 25</t>
         </is>
       </c>
       <c r="Q27" s="4" t="inlineStr">
@@ -2437,7 +2437,7 @@
         <v>5376.52</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>396.6</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>1500</v>
@@ -2491,7 +2491,7 @@
         <v>484.7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>396.58</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>325.63</v>
+        <v>1118.81</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2911,7 +2911,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3105,13 +3105,13 @@
         <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>396.6</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>250</v>
+        <v>-146.6</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>1.5864</v>
       </c>
     </row>
     <row r="9">
@@ -3225,13 +3225,13 @@
         <v>68268</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>396.58</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>68268</v>
+        <v>67871.42</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.005809163883517899</v>
       </c>
     </row>
     <row r="14">
@@ -3268,13 +3268,13 @@
         <v>74230.31300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>325.63</v>
+        <v>1118.81</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>73904.683</v>
+        <v>73111.503</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.004386752350081024</v>
+        <v>0.01507214444858935</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
+        <v>155.91</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2869,7 +2869,7 @@
         <v>23543.77</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>155.91</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>15000</v>
@@ -2886,7 +2886,7 @@
         <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1118.81</v>
+        <v>1274.72</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3225,13 +3225,13 @@
         <v>68268</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>396.58</v>
+        <v>552.49</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>67871.42</v>
+        <v>67715.50999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.005809163883517899</v>
+        <v>0.008092957168805297</v>
       </c>
     </row>
     <row r="14">
@@ -3268,13 +3268,13 @@
         <v>74230.31300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1118.81</v>
+        <v>1274.72</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>73111.503</v>
+        <v>72955.59299999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.01507214444858935</v>
+        <v>0.01717249932652177</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>0</v>
+        <v>183.05</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="Q27" s="4" t="inlineStr">
@@ -2464,7 +2464,7 @@
         <v>3518.65</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>183.05</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1274.72</v>
+        <v>1457.77</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3105,13 +3105,13 @@
         <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>396.6</v>
+        <v>579.65</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-146.6</v>
+        <v>-329.65</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.5864</v>
+        <v>2.3186</v>
       </c>
     </row>
     <row r="9">
@@ -3268,13 +3268,13 @@
         <v>74230.31300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1274.72</v>
+        <v>1457.77</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>72955.59299999999</v>
+        <v>72772.54300000001</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.01717249932652177</v>
+        <v>0.01963847303190005</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>155.91</v>
+        <v>161.62</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2869,7 +2869,7 @@
         <v>23543.77</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>155.91</v>
+        <v>161.62</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>15000</v>
@@ -2886,7 +2886,7 @@
         <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1457.77</v>
+        <v>1463.48</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2911,7 +2911,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3225,13 +3225,13 @@
         <v>68268</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>552.49</v>
+        <v>558.2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>67715.50999999999</v>
+        <v>67709.8</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.008092957168805297</v>
+        <v>0.0081765981133181</v>
       </c>
     </row>
     <row r="14">
@@ -3268,13 +3268,13 @@
         <v>74230.31300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1457.77</v>
+        <v>1463.48</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>72772.54300000001</v>
+        <v>72766.83300000001</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.01963847303190005</v>
+        <v>0.0197153957844688</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>2544.36</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>4392.79</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>5410.23</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>1 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>4 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>2544.36</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -2464,7 +2464,7 @@
         <v>3518.65</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>183.05</v>
+        <v>4575.84</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>5410.23</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>500</v>
@@ -2886,7 +2886,7 @@
         <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1463.48</v>
+        <v>13810.86</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,7 +2909,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3201,13 +3201,13 @@
         <v>254</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>4392.79</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>254</v>
+        <v>-4138.79</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>17.29444881889764</v>
       </c>
     </row>
     <row r="13">
@@ -3225,13 +3225,13 @@
         <v>68268</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>558.2</v>
+        <v>8512.790000000001</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>67709.8</v>
+        <v>59755.21</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.0081765981133181</v>
+        <v>0.1246966367844378</v>
       </c>
     </row>
     <row r="14">
@@ -3268,13 +3268,13 @@
         <v>74230.31300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1463.48</v>
+        <v>13810.86</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>72766.83300000001</v>
+        <v>60419.453</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.0197153957844688</v>
+        <v>0.1860541797796272</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -756,31 +756,31 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>113.32</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>140.8</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>155.39</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>216.79</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>1134.21</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>189.2</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>10210.41</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5410.23</v>
+        <v>6670.46</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>325.63</v>
@@ -1857,10 +1857,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1773.76</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>9836.83</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2061,57 +2061,57 @@
     <row r="27">
       <c r="C27" s="4" t="inlineStr">
         <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>1 de 25</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>2 de 25</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>1 de 25</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>3 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>4 de 25</t>
+          <t>7 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>1856.61</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1000</v>
@@ -2572,7 +2572,7 @@
         <v>1033.12</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>10399.61</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1000</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5410.23</v>
+        <v>6670.46</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>500</v>
@@ -2788,7 +2788,7 @@
         <v>-142.56</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>325.63</v>
+        <v>12044.22</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2886,7 +2886,7 @@
         <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>13810.86</v>
+        <v>39045.9</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,8 +2909,8 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2961,13 +2961,13 @@
         <v>136.08</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>136.08</v>
+        <v>28.08000000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>0.7936507936507936</v>
       </c>
     </row>
     <row r="3">
@@ -3009,13 +3009,13 @@
         <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>199.5</v>
+        <v>125.21</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>0.3723809523809524</v>
       </c>
     </row>
     <row r="5">
@@ -3033,13 +3033,13 @@
         <v>172.82</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>113.32</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>172.82</v>
+        <v>59.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>0.6557111445434556</v>
       </c>
     </row>
     <row r="6">
@@ -3081,13 +3081,13 @@
         <v>263.55</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>263.55</v>
+        <v>-66.44999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1.252134319863403</v>
       </c>
     </row>
     <row r="8">
@@ -3153,13 +3153,13 @@
         <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>155.39</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>203.763</v>
+        <v>48.37300000000002</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.7626016499560764</v>
       </c>
     </row>
     <row r="11">
@@ -3177,13 +3177,13 @@
         <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>21.81</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115</v>
+        <v>93.19</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.1896521739130435</v>
       </c>
     </row>
     <row r="12">
@@ -3201,13 +3201,13 @@
         <v>254</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4392.79</v>
+        <v>6383.34</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-4138.79</v>
+        <v>-6129.34</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>17.29444881889764</v>
+        <v>25.13125984251969</v>
       </c>
     </row>
     <row r="13">
@@ -3225,13 +3225,13 @@
         <v>68268</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8512.790000000001</v>
+        <v>30954.47</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>59755.21</v>
+        <v>37313.53</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1246966367844378</v>
+        <v>0.4534257631686882</v>
       </c>
     </row>
     <row r="14">
@@ -3268,13 +3268,13 @@
         <v>74230.31300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>13810.86</v>
+        <v>39045.9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>60419.453</v>
+        <v>35184.413</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1860541797796272</v>
+        <v>0.5260101759236823</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1860,7 +1860,7 @@
         <v>1773.76</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>9836.83</v>
+        <v>8967.59</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>-142.56</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>12044.22</v>
+        <v>11174.98</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2886,7 +2886,7 @@
         <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>39045.9</v>
+        <v>38176.66</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3225,13 +3225,13 @@
         <v>68268</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>30954.47</v>
+        <v>30085.23</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37313.53</v>
+        <v>38182.77</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.4534257631686882</v>
+        <v>0.4406930040428898</v>
       </c>
     </row>
     <row r="14">
@@ -3268,13 +3268,13 @@
         <v>74230.31300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>39045.9</v>
+        <v>38176.66</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>35184.413</v>
+        <v>36053.653</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5260101759236823</v>
+        <v>0.5143001350405191</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>161.62</v>
+        <v>18379.73</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2869,7 +2869,7 @@
         <v>23543.77</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>161.62</v>
+        <v>18379.73</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>15000</v>
@@ -2886,7 +2886,7 @@
         <v>50050.21</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>38176.66</v>
+        <v>56394.77</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3225,13 +3225,13 @@
         <v>68268</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>30085.23</v>
+        <v>50929.07</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>38182.77</v>
+        <v>17338.93</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.4406930040428898</v>
+        <v>0.7460167281889025</v>
       </c>
     </row>
     <row r="14">
@@ -3268,13 +3268,13 @@
         <v>74230.31300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>38176.66</v>
+        <v>59020.5</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>36053.653</v>
+        <v>15209.813</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5143001350405191</v>
+        <v>0.7950997054262723</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -756,31 +756,31 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>74.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>113.32</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>140.8</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>155.39</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>216.79</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1134.21</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2544.36</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>396.6</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>4392.79</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>183.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>396.58</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>189.2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10210.41</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6670.46</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>325.63</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -1857,10 +1857,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1773.76</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8967.59</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>18379.73</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2061,17 +2061,17 @@
     <row r="27">
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>3 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>7 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="Q27" s="4" t="inlineStr">
@@ -2156,10 +2156,10 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2176,22 +2176,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2215,10 +2215,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>337.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>337.8</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -2299,10 +2299,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>1856.61</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1856.61</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1000</v>
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>10645.56</v>
+        <v>760.3200000000001</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>760.3200000000001</v>
+        <v>141.53</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>141.53</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>2544.36</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2544.36</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>5376.52</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>5376.52</v>
+        <v>396.6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>396.6</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>1500</v>
@@ -2458,13 +2458,13 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>3518.65</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3518.65</v>
+        <v>4575.84</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4575.84</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2482,16 +2482,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>767.9400000000001</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>767.9400000000001</v>
+        <v>484.7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>484.7</v>
+        <v>396.58</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>396.58</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -2509,13 +2509,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>18531.43</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>15756.68</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>15756.68</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>793.76</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1033.12</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1033.12</v>
+        <v>10399.61</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>10399.61</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1000</v>
@@ -2623,10 +2623,10 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>6670.46</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6670.46</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>500</v>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3757.05</v>
+        <v>4048.19</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4048.19</v>
+        <v>-142.56</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-142.56</v>
+        <v>11174.98</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>11174.98</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2860,16 +2860,16 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>16458.65</v>
+        <v>4436.21</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4436.21</v>
+        <v>23543.77</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>23543.77</v>
+        <v>18379.73</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>18379.73</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>15000</v>
@@ -2877,16 +2877,16 @@
     </row>
     <row r="27">
       <c r="C27" s="6" t="n">
-        <v>50186.45</v>
+        <v>10012.66</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>10012.66</v>
+        <v>50050.21</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>50050.21</v>
+        <v>56394.77</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>56394.77</v>
+        <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2909,9 +2909,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2958,16 +2958,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>136.08</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>28.08000000000001</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.7936507936507936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2982,16 +2982,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3800</v>
+        <v>1223</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>325.63</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3474.37</v>
+        <v>1223</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.08569210526315789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3009,13 +3009,13 @@
         <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>74.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>125.21</v>
+        <v>199.5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.3723809523809524</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3033,13 +3033,13 @@
         <v>172.82</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>113.32</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>59.5</v>
+        <v>172.82</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.6557111445434556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INODOROS</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>240</v>
+        <v>263.55</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>240</v>
+        <v>263.55</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -3074,20 +3074,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>263.55</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-66.44999999999999</v>
+        <v>250</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.252134319863403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>579.65</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-329.65</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2.3186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3122,17 +3122,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>203.763</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>203.763</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3146,20 +3146,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>203.763</v>
+        <v>115</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>155.39</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>48.37300000000002</v>
+        <v>115</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7626016499560764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3170,20 +3170,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>115</v>
+        <v>2105</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>21.81</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>93.19</v>
+        <v>2105</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1896521739130435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>254</v>
+        <v>39250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6383.34</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-6129.34</v>
+        <v>39250</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>25.13125984251969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3218,20 +3218,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>68268</v>
+        <v>327.6</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>50929.07</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17338.93</v>
+        <v>327.6</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.7460167281889025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3242,17 +3242,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+          <t>SAL SOLUBLE</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>327.6</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>327.6</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -3265,16 +3265,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>74230.31300000001</v>
+        <v>44110.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>59020.5</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15209.813</v>
+        <v>44110.233</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.7950997054262723</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>1292.54</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0</v>
+        <v>550.63</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
@@ -2111,22 +2111,22 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>0 de 25</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>0 de 25</t>
+          <t>1 de 25</t>
         </is>
       </c>
       <c r="Q27" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>1843.17</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1000</v>
@@ -2886,7 +2886,7 @@
         <v>56394.77</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0</v>
+        <v>1843.17</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,9 +2909,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3081,13 +3081,13 @@
         <v>250</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>550.63</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>250</v>
+        <v>-300.63</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>2.20252</v>
       </c>
     </row>
     <row r="8">
@@ -3201,13 +3201,13 @@
         <v>39250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1292.54</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>39250</v>
+        <v>37957.46</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.03293095541401274</v>
       </c>
     </row>
     <row r="13">
@@ -3268,13 +3268,13 @@
         <v>44110.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1843.17</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>44110.233</v>
+        <v>42267.06299999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>0.04178554214392837</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>-7097.63</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>-145.19</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2572,7 +2572,7 @@
         <v>10399.61</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>-7097.63</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1000</v>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>-145.19</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>500</v>
@@ -2886,7 +2886,7 @@
         <v>56394.77</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1843.17</v>
+        <v>-5399.65</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,7 +2909,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3201,13 +3201,13 @@
         <v>39250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1292.54</v>
+        <v>-5950.28</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>37957.46</v>
+        <v>45200.28</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.03293095541401274</v>
+        <v>-0.1515994904458599</v>
       </c>
     </row>
     <row r="13">
@@ -3268,13 +3268,13 @@
         <v>44110.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1843.17</v>
+        <v>-5399.65</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>42267.06299999999</v>
+        <v>49509.88299999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.04178554214392837</v>
+        <v>-0.1224126383553676</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>5382.95</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>5382.95</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>12870</v>
@@ -2886,7 +2886,7 @@
         <v>56394.77</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-5399.65</v>
+        <v>-16.70000000000022</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,9 +2909,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3201,13 +3201,13 @@
         <v>39250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-5950.28</v>
+        <v>-567.33</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45200.28</v>
+        <v>39817.33</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.1515994904458599</v>
+        <v>-0.01445426751592357</v>
       </c>
     </row>
     <row r="13">
@@ -3268,13 +3268,13 @@
         <v>44110.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-5399.65</v>
+        <v>-16.70000000000005</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>49509.88299999999</v>
+        <v>44126.933</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.1224126383553676</v>
+        <v>-0.0003785969573092041</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>110.19</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>2 de 25</t>
+          <t>3 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2788,7 +2788,7 @@
         <v>11174.98</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>110.19</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2886,7 +2886,7 @@
         <v>56394.77</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-16.70000000000022</v>
+        <v>93.48999999999978</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -3201,13 +3201,13 @@
         <v>39250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-567.33</v>
+        <v>-457.14</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>39817.33</v>
+        <v>39707.14</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.01445426751592357</v>
+        <v>-0.01164687898089172</v>
       </c>
     </row>
     <row r="13">
@@ -3268,13 +3268,13 @@
         <v>44110.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-16.70000000000005</v>
+        <v>93.49000000000001</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>44126.933</v>
+        <v>44016.74299999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.0003785969573092041</v>
+        <v>0.00211946284663697</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>103.94</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-145.19</v>
+        <v>131.05</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>3 de 25</t>
+          <t>5 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>103.94</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-145.19</v>
+        <v>131.05</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>500</v>
@@ -2886,7 +2886,7 @@
         <v>56394.77</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>93.48999999999978</v>
+        <v>473.6699999999998</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,9 +2909,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3201,13 +3201,13 @@
         <v>39250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-457.14</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>39707.14</v>
+        <v>39326.96</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.01164687898089172</v>
+        <v>-0.001960764331210191</v>
       </c>
     </row>
     <row r="13">
@@ -3268,13 +3268,13 @@
         <v>44110.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>93.49000000000001</v>
+        <v>473.67</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>44016.74299999999</v>
+        <v>43636.56299999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.00211946284663697</v>
+        <v>0.01073832459692516</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>-1260.23</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
         <v>6670.46</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>-1260.23</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>500</v>
@@ -2886,7 +2886,7 @@
         <v>56394.77</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>473.6699999999998</v>
+        <v>-786.5600000000002</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>
@@ -2909,9 +2909,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3201,13 +3201,13 @@
         <v>39250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-76.95999999999999</v>
+        <v>-1337.19</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>39326.96</v>
+        <v>40587.19</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.001960764331210191</v>
+        <v>-0.03406853503184713</v>
       </c>
     </row>
     <row r="13">
@@ -3268,13 +3268,13 @@
         <v>44110.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>473.67</v>
+        <v>-786.5600000000001</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>43636.56299999999</v>
+        <v>44896.793</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.01073832459692516</v>
+        <v>-0.01783168998449861</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>103.94</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1292.54</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>550.63</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5382.95</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>-7097.63</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-1260.23</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>131.05</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>110.19</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>5 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>0 de 25</t>
         </is>
       </c>
       <c r="Q27" s="4" t="inlineStr">
@@ -2156,10 +2156,10 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2176,22 +2176,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>337.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>337.8</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>103.94</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>103.94</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -2296,10 +2296,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1856.61</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1856.61</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -2326,10 +2326,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1843.17</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1843.17</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1000</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>760.3200000000001</v>
+        <v>141.53</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>141.53</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -2404,10 +2404,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>2544.36</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2544.36</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>5376.52</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5376.52</v>
+        <v>396.6</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>396.6</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>3518.65</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3518.65</v>
+        <v>4575.84</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4575.84</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>767.9400000000001</v>
+        <v>484.7</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>484.7</v>
+        <v>396.58</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>396.58</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -2509,16 +2509,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>15756.68</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>15756.68</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>5382.95</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>5382.95</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>12870</v>
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>1033.12</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1033.12</v>
+        <v>10399.61</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10399.61</v>
+        <v>-7097.63</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-7097.63</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1000</v>
@@ -2620,13 +2620,13 @@
         <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>6670.46</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6670.46</v>
+        <v>-1260.23</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1260.23</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>500</v>
@@ -2758,10 +2758,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>131.05</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>131.05</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>500</v>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>4048.19</v>
+        <v>-142.56</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>-142.56</v>
+        <v>11174.98</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11174.98</v>
+        <v>110.19</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>110.19</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -2860,13 +2860,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4436.21</v>
+        <v>23543.77</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>23543.77</v>
+        <v>18379.73</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>18379.73</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
@@ -2877,16 +2877,16 @@
     </row>
     <row r="27">
       <c r="C27" s="6" t="n">
-        <v>10012.66</v>
+        <v>50050.21</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>50050.21</v>
+        <v>56394.77</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>56394.77</v>
+        <v>-786.5600000000002</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-786.5600000000002</v>
+        <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2151,11 +2151,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -2208,17 +2208,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARCOS GOMEZ CONSTRUCCIONES CIA. LTDA.</t>
+          <t>ABRIL NARANJO NANCY MARIBEL</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>337.8</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>103.94</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -2235,17 +2235,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BARRAGAN PUENTE NATALY CAROLINA</t>
+          <t>ARCOS GOMEZ CONSTRUCCIONES CIA. LTDA.</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>337.8</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>103.94</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BECERRA FARIAS ROSA DAYANA</t>
+          <t>BARRAGAN PUENTE NATALY CAROLINA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2289,14 +2289,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BELTRAN ESPINOZA SONIA SARITA</t>
+          <t>BECERRA FARIAS ROSA DAYANA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1856.61</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -2316,17 +2316,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
+          <t>BELTRAN ESPINOZA SONIA SARITA</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1856.61</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1843.17</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2343,11 +2343,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CERAMICAS AL COSTO S.A.S.</t>
+          <t>BRAZALES BASTIDAS MERCY JANETH</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>141.53</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CERAMICCENTER CIA. LTDA.</t>
+          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2380,13 +2380,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1843.17</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -2397,14 +2397,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
+          <t>CENYCA S.C.C.</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2544.36</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -2424,14 +2424,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CONZA VEGA FRANCO BLADYMIR</t>
+          <t>CERAMICAS AL COSTO S.A.S.</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5376.52</v>
+        <v>141.53</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>396.6</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="11">
@@ -2451,14 +2451,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CULMA OVIEDO NINI JOHANA</t>
+          <t>CERAMICCENTER CIA. LTDA.</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3518.65</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4575.84</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -2478,14 +2478,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DDH S.A.S.</t>
+          <t>CHUQUIZAN MUESES MARIA ROSARIO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>484.7</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>396.58</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -2505,23 +2505,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F.V - AREA ANDINA S.A.</t>
+          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>15756.68</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>2544.36</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5382.95</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>12870</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2532,14 +2532,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FERRIACABADOS MACONSE</t>
+          <t>CONZA VEGA FRANCO BLADYMIR</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>5376.52</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>396.6</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15">
@@ -2559,23 +2559,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
+          <t>CORTEZ GALARZA MARIA ISABEL</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1033.12</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10399.61</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-7097.63</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2586,14 +2586,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>CULMA OVIEDO NINI JOHANA</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>3518.65</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>4575.84</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -2613,23 +2613,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>DDH S.A.S.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>484.7</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6670.46</v>
+        <v>396.58</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-1260.23</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2640,23 +2640,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>F.V - AREA ANDINA S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>15756.68</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>5382.95</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>12870</v>
       </c>
     </row>
     <row r="19">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>FERRIACABADOS MACONSE</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>FERRONORTECORP CIA. LTDA.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2721,23 +2721,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>1033.12</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>10399.61</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>-7097.63</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -2758,13 +2758,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>131.05</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2775,23 +2775,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>MACAS ROMERO HERNAN TULIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-142.56</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>11174.98</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>110.19</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2802,14 +2802,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>MALO LARREA JAVIER EDUARDO</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>2625.73</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -2829,23 +2829,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>6670.46</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>-1260.23</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26">
@@ -2856,39 +2856,498 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MORALES CORTEZ KLEVER VINICIO</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NIZA ARIAS YOSELIN EDITH</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NOGALES DOTA ALEX DAVID</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PUCHAICELA AGUINZACA JENNY GEOVANNA</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SAAVEDRA &amp; SANTANDER CIA.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SOCIEDAD CIVIL COMERCIAL FERRETERIA MACONSE</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>131.05</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>-142.56</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>11174.98</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>110.19</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>VILLEGAS BAYAS NANCY CECILIA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C42" s="2" t="n">
         <v>23543.77</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D42" s="2" t="n">
         <v>18379.73</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="n">
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="27">
-      <c r="C27" s="6" t="n">
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="6" t="n">
         <v>50050.21</v>
       </c>
-      <c r="D27" s="6" t="n">
-        <v>56394.77</v>
-      </c>
-      <c r="E27" s="6" t="n">
+      <c r="D44" s="6" t="n">
+        <v>59020.5</v>
+      </c>
+      <c r="E44" s="6" t="n">
         <v>-786.5600000000002</v>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6" t="n">
+      <c r="F44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6" t="n">
         <v>38870</v>
       </c>
     </row>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>MALO LARREA JAVIER EDUARDO</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>NIZA ARIAS YOSELIN EDITH</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2006,137 +2006,377 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="R27" s="4" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
         </is>
       </c>
     </row>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>63.92</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>356.4</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0</v>
+        <v>394.63</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2331,27 +2331,27 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2488,7 +2488,7 @@
         <v>103.94</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>63.92</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
         <v>-7097.63</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>356.4</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1000</v>
@@ -3379,7 +3379,7 @@
         <v>131.05</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>394.63</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>500</v>
@@ -3585,7 +3585,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0</v>
+        <v>814.9499999999999</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>939.08</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>3 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2893,7 +2893,7 @@
         <v>5382.95</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>939.08</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>12870</v>
@@ -3585,7 +3585,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>814.9499999999999</v>
+        <v>1754.03</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>939.08</v>
+        <v>976.35</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>5382.95</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>939.08</v>
+        <v>976.35</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>12870</v>
@@ -3585,7 +3585,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1754.03</v>
+        <v>1791.3</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>146.97</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0</v>
+        <v>146.97</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>15000</v>
@@ -3585,7 +3585,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1791.3</v>
+        <v>1938.27</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>2052.09</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>3 de 29</t>
+          <t>4 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3082,7 +3082,7 @@
         <v>-1260.23</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>2052.09</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>500</v>
@@ -3585,7 +3585,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1938.27</v>
+        <v>3990.36</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>154.22</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>4 de 29</t>
+          <t>5 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>154.22</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>2500</v>
@@ -3585,7 +3585,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>3990.36</v>
+        <v>4144.58</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>38870</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -3602,15 +3602,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3657,13 +3657,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -3681,13 +3681,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1223</v>
+        <v>2450</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1223</v>
+        <v>2450</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -3705,13 +3705,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>199.5</v>
+        <v>198</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>199.5</v>
+        <v>198</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -3729,13 +3729,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>172.82</v>
+        <v>133.5</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>172.82</v>
+        <v>133.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3753,16 +3753,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>263.55</v>
+        <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>356.4</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>263.55</v>
+        <v>-44.39999999999998</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1.142307692307692</v>
       </c>
     </row>
     <row r="7">
@@ -3780,13 +3780,13 @@
         <v>250</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>550.63</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-300.63</v>
+        <v>250</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2.20252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3825,13 +3825,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>203.763</v>
+        <v>400</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>203.763</v>
+        <v>400</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2105</v>
+        <v>574</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>146.97</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2105</v>
+        <v>427.03</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.2560452961672474</v>
       </c>
     </row>
     <row r="12">
@@ -3897,16 +3897,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>39250</v>
+        <v>35465</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-1337.19</v>
+        <v>3641.21</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>40587.19</v>
+        <v>31823.79</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.03406853503184713</v>
+        <v>0.1026705202312139</v>
       </c>
     </row>
     <row r="13">
@@ -3921,59 +3921,35 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>327.6</v>
+        <v>228</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>327.6</v>
+        <v>228</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SAL SOLUBLE</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>40352.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>4144.58</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>36207.92</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>44110.233</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>-786.5600000000001</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>44896.793</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>-0.01783168998449861</v>
+        <v>0.1027093736447556</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2220,7 +2220,7 @@
         <v>146.97</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0</v>
+        <v>16853.73</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>5 de 29</t>
+          <t>6 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>146.97</v>
+        <v>17000.7</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>15000</v>
@@ -3585,7 +3585,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>4144.58</v>
+        <v>20998.31</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>38870</v>
@@ -3608,7 +3608,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3900,13 +3900,13 @@
         <v>35465</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3641.21</v>
+        <v>20494.94</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>31823.79</v>
+        <v>14970.06</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1026705202312139</v>
+        <v>0.5778920062032989</v>
       </c>
     </row>
     <row r="13">
@@ -3943,13 +3943,13 @@
         <v>40352.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4144.58</v>
+        <v>20998.31</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>36207.92</v>
+        <v>19354.19</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1027093736447556</v>
+        <v>0.5203719719967783</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>63.92</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>394.63</v>
+        <v>1183.89</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>103.94</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>63.92</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -3379,7 +3379,7 @@
         <v>131.05</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>394.63</v>
+        <v>1183.89</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>500</v>
@@ -3585,7 +3585,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>20998.31</v>
+        <v>21813.55</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>38870</v>
@@ -3900,13 +3900,13 @@
         <v>35465</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>20494.94</v>
+        <v>21310.18</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14970.06</v>
+        <v>14154.82</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5778920062032989</v>
+        <v>0.6008791766530382</v>
       </c>
     </row>
     <row r="13">
@@ -3943,13 +3943,13 @@
         <v>40352.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>20998.31</v>
+        <v>21813.55</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>19354.19</v>
+        <v>18538.95</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.5203719719967783</v>
+        <v>0.5405749333994176</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>146.97</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0</v>
+        <v>16853.73</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
+          <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2217,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>146.97</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>16853.73</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
@@ -2239,144 +2239,84 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>1 de 29</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>1 de 29</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>6 de 29</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="R31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>1 de 28</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>1 de 28</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>6 de 28</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>0 de 28</t>
         </is>
       </c>
     </row>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>167.85</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>103.94</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>167.85</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>21813.55</v>
+        <v>21891.5</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>38870</v>
@@ -3840,13 +3840,13 @@
         <v>35465</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>21310.18</v>
+        <v>21388.13</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14154.82</v>
+        <v>14076.87</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6008791766530382</v>
+        <v>0.6030771182856337</v>
       </c>
     </row>
     <row r="13">
@@ -3883,13 +3883,13 @@
         <v>40352.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>21813.55</v>
+        <v>21891.5</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>18538.95</v>
+        <v>18461</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.5405749333994176</v>
+        <v>0.5425066600582368</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>807.21</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>GOMEZ VALDIVIESO CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>1874.31</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MALO LARREA JAVIER EDUARDO</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>MALO LARREA JAVIER EDUARDO</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2052.09</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>2052.09</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NIZA ARIAS YOSELIN EDITH</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>NIZA ARIAS YOSELIN EDITH</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1183.89</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>1183.89</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>146.97</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>16853.73</v>
+        <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
@@ -2186,137 +2186,197 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>ZAMBRANO ANGELA MARIA</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>146.97</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>16853.73</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>1 de 28</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>1 de 28</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>6 de 28</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="O30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="P30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
-        </is>
-      </c>
-      <c r="R30" s="4" t="inlineStr">
-        <is>
-          <t>0 de 28</t>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>2 de 29</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>7 de 29</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2779,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>807.21</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -2928,7 +2988,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>GOMEZ VALDIVIESO CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -2941,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>2289.43</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -2955,7 +3015,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MACAS ROMERO HERNAN TULIO</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2982,14 +3042,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MALO LARREA JAVIER EDUARDO</t>
+          <t>MACAS ROMERO HERNAN TULIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2625.73</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -3009,23 +3069,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>MALO LARREA JAVIER EDUARDO</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6670.46</v>
+        <v>2625.73</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-1260.23</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2052.09</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3036,23 +3096,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>6670.46</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>-1260.23</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>2052.09</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="27">
@@ -3063,7 +3123,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MORALES CORTEZ KLEVER VINICIO</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -3090,7 +3150,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>MORALES CORTEZ KLEVER VINICIO</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -3117,7 +3177,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -3144,7 +3204,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NIZA ARIAS YOSELIN EDITH</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3171,7 +3231,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NOGALES DOTA ALEX DAVID</t>
+          <t>NIZA ARIAS YOSELIN EDITH</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -3198,7 +3258,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PUCHAICELA AGUINZACA JENNY GEOVANNA</t>
+          <t>NOGALES DOTA ALEX DAVID</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -3225,7 +3285,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>PUCHAICELA AGUINZACA JENNY GEOVANNA</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -3252,7 +3312,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAAVEDRA &amp; SANTANDER CIA.</t>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -3279,7 +3339,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SOCIEDAD CIVIL COMERCIAL FERRETERIA MACONSE</t>
+          <t>SAAVEDRA &amp; SANTANDER CIA.</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -3306,7 +3366,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>SOCIEDAD CIVIL COMERCIAL FERRETERIA MACONSE</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -3316,13 +3376,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>131.05</v>
+        <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1183.89</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3333,23 +3393,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>-142.56</v>
+        <v>0</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>11174.98</v>
+        <v>0</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>110.19</v>
+        <v>131.05</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0</v>
+        <v>1183.89</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="38">
@@ -3360,23 +3420,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0</v>
+        <v>-142.56</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0</v>
+        <v>11174.98</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>110.19</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="39">
@@ -3387,7 +3447,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -3414,7 +3474,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -3441,7 +3501,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VILLEGAS BAYAS NANCY CECILIA</t>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -3468,23 +3528,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
+          <t>VILLEGAS BAYAS NANCY CECILIA</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>23543.77</v>
+        <v>0</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>18379.73</v>
+        <v>0</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>17000.7</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3495,39 +3555,66 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>ZAMBRANO ANGELA MARIA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>23543.77</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>18379.73</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>17000.7</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" s="6" t="n">
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" s="6" t="n">
         <v>50050.21</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D45" s="6" t="n">
         <v>59020.5</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E45" s="6" t="n">
         <v>-786.5600000000002</v>
       </c>
-      <c r="F44" s="6" t="n">
-        <v>21891.5</v>
-      </c>
-      <c r="G44" s="6" t="n">
+      <c r="F45" s="6" t="n">
+        <v>24988.14</v>
+      </c>
+      <c r="G45" s="6" t="n">
         <v>38870</v>
       </c>
     </row>
@@ -3792,13 +3879,13 @@
         <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>415.12</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>220</v>
+        <v>-195.12</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.886909090909091</v>
       </c>
     </row>
     <row r="11">
@@ -3816,13 +3903,13 @@
         <v>574</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>146.97</v>
+        <v>954.1799999999999</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>427.03</v>
+        <v>-380.1799999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.2560452961672474</v>
+        <v>1.662334494773519</v>
       </c>
     </row>
     <row r="12">
@@ -3840,13 +3927,13 @@
         <v>35465</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>21388.13</v>
+        <v>23262.44</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14076.87</v>
+        <v>12202.56</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6030771182856337</v>
+        <v>0.6559266882842238</v>
       </c>
     </row>
     <row r="13">
@@ -3883,13 +3970,13 @@
         <v>40352.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>21891.5</v>
+        <v>24988.14</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>18461</v>
+        <v>15364.36</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.5425066600582368</v>
+        <v>0.619246391177746</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>807.21</v>
+        <v>1614.42</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>146.97</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>16853.73</v>
+        <v>55761.49</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>807.21</v>
+        <v>1614.42</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>17000.7</v>
+        <v>55908.46</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>15000</v>
@@ -3612,7 +3612,7 @@
         <v>-786.5600000000002</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>24988.14</v>
+        <v>64703.11</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>38870</v>
@@ -3635,9 +3635,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3903,13 +3903,13 @@
         <v>574</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>954.1799999999999</v>
+        <v>1761.39</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-380.1799999999999</v>
+        <v>-1187.39</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.662334494773519</v>
+        <v>3.068623693379791</v>
       </c>
     </row>
     <row r="12">
@@ -3927,13 +3927,13 @@
         <v>35465</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>23262.44</v>
+        <v>62170.2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12202.56</v>
+        <v>-26705.2</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6559266882842238</v>
+        <v>1.753001550824757</v>
       </c>
     </row>
     <row r="13">
@@ -3970,13 +3970,13 @@
         <v>40352.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>24988.14</v>
+        <v>64703.11</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15364.36</v>
+        <v>-24350.61</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.619246391177746</v>
+        <v>1.603447370051422</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>167.85</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>154.22</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1614.42</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>976.35</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>356.4</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1874.31</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2052.09</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1183.89</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>VARIEDADES-PAS SAS</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2217,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>146.97</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>55761.49</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
@@ -2246,137 +2246,197 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>ZAMBRANO ANGELA MARIA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>1 de 29</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>2 de 29</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>7 de 29</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="R31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2399,7 +2459,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2416,22 +2476,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2479,16 +2539,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>337.8</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>103.94</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>103.94</v>
+        <v>167.85</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>167.85</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -2560,10 +2620,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>1856.61</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1856.61</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -2617,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>1843.17</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1843.17</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -2668,16 +2728,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>141.53</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>154.22</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>154.22</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>2500</v>
@@ -2749,10 +2809,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>2544.36</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2544.36</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -2776,10 +2836,10 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5376.52</v>
+        <v>396.6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>396.6</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -2830,16 +2890,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>3518.65</v>
+        <v>4575.84</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4575.84</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>1614.42</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1614.42</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -2857,10 +2917,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>484.7</v>
+        <v>396.58</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>396.58</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -2884,16 +2944,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>15756.68</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>5382.95</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5382.95</v>
+        <v>976.35</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>976.35</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>12870</v>
@@ -2965,16 +3025,16 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1033.12</v>
+        <v>10399.61</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10399.61</v>
+        <v>-7097.63</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-7097.63</v>
+        <v>356.4</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>356.4</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1000</v>
@@ -2998,10 +3058,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>2289.43</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2289.43</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3073,10 +3133,10 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0</v>
+        <v>2625.73</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2625.73</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -3100,16 +3160,16 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>6670.46</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6670.46</v>
+        <v>-1260.23</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-1260.23</v>
+        <v>2052.09</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2052.09</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>500</v>
@@ -3400,13 +3460,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0</v>
+        <v>131.05</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>131.05</v>
+        <v>1183.89</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>1183.89</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>500</v>
@@ -3424,13 +3484,13 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-142.56</v>
+        <v>11174.98</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>11174.98</v>
+        <v>110.19</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>110.19</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
@@ -3447,7 +3507,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
+          <t>VARIEDADES-PAS SAS</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -3457,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0</v>
+        <v>294.49</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -3474,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -3501,7 +3561,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -3528,7 +3588,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VILLEGAS BAYAS NANCY CECILIA</t>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3555,23 +3615,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
+          <t>VILLEGAS BAYAS NANCY CECILIA</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>23543.77</v>
+        <v>0</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>18379.73</v>
+        <v>0</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>55908.46</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3582,39 +3642,66 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>ZAMBRANO ANGELA MARIA</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>18379.73</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>55908.46</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" s="6" t="n">
-        <v>50050.21</v>
-      </c>
-      <c r="D45" s="6" t="n">
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="6" t="n">
         <v>59020.5</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="D46" s="6" t="n">
         <v>-786.5600000000002</v>
       </c>
-      <c r="F45" s="6" t="n">
-        <v>64703.11</v>
-      </c>
-      <c r="G45" s="6" t="n">
+      <c r="E46" s="6" t="n">
+        <v>64997.6</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="6" t="n">
         <v>38870</v>
       </c>
     </row>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -3716,15 +3716,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>122</v>
+        <v>500</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>122</v>
+        <v>500</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -3870,13 +3870,13 @@
         <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>356.4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-44.39999999999998</v>
+        <v>312</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.142307692307692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3966,13 +3966,13 @@
         <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>415.12</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-195.12</v>
+        <v>220</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.886909090909091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3983,20 +3983,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>574</v>
+        <v>38234</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1761.39</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1187.39</v>
+        <v>38234</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.068623693379791</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4007,63 +4007,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>35465</v>
+        <v>570</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>62170.2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-26705.2</v>
+        <v>570</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.753001550824757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>228</v>
+        <v>43267.5</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>228</v>
+        <v>43267.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>40352.5</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>64703.11</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-24350.61</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1.603447370051422</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="6">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11">
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="15">
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="17">
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12870</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="19">
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22">
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="23">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="26">
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27">
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38">
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="39">
@@ -3658,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>15000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="45">
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>38870</v>
+        <v>41650</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2088,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>289.94</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0</v>
@@ -2100,10 +2100,10 @@
         <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
+        <v>8339.67</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0</v>
+        <v>914.4</v>
       </c>
       <c r="O27" s="2" t="n">
         <v>0</v>
@@ -2391,32 +2391,32 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>0 de 30</t>
+          <t>1 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>0 de 30</t>
+          <t>1 de 30</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3520,7 +3520,7 @@
         <v>294.49</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0</v>
+        <v>9544.01</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>64997.6</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0</v>
+        <v>9544.01</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>41650</v>
@@ -3722,9 +3722,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3870,13 +3870,13 @@
         <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>289.94</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>312</v>
+        <v>22.06</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>0.9292948717948718</v>
       </c>
     </row>
     <row r="7">
@@ -3990,13 +3990,13 @@
         <v>38234</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>8339.67</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>38234</v>
+        <v>29894.33</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.2181218287388189</v>
       </c>
     </row>
     <row r="12">
@@ -4014,13 +4014,13 @@
         <v>570</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>914.4</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>570</v>
+        <v>-344.4</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1.60421052631579</v>
       </c>
     </row>
     <row r="13">
@@ -4033,13 +4033,13 @@
         <v>43267.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>9544.01</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>43267.5</v>
+        <v>33723.49</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.2205814988155082</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2451,7 +2451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>VILLEGAS BAYAS NANCY CECILIA</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3615,23 +3615,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VILLEGAS BAYAS NANCY CECILIA</t>
+          <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0</v>
+        <v>18379.73</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0</v>
+        <v>55908.46</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="44">
@@ -3642,66 +3642,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
+          <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>18379.73</v>
+        <v>0</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>55908.46</v>
+        <v>0</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" s="6" t="n">
+      <c r="C45" s="6" t="n">
         <v>59020.5</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D45" s="6" t="n">
         <v>-786.5600000000002</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E45" s="6" t="n">
         <v>64997.6</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F45" s="6" t="n">
         <v>9544.01</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G45" s="6" t="n">
         <v>41650</v>
       </c>
     </row>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2451,11 +2451,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -2508,23 +2508,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABRIL NARANJO NANCY MARIBEL</t>
+          <t>ARCOS GOMEZ CONSTRUCCIONES CIA. LTDA.</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>103.94</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>167.85</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
@@ -2535,23 +2535,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARCOS GOMEZ CONSTRUCCIONES CIA. LTDA.</t>
+          <t>BARRAGAN PUENTE NATALY CAROLINA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>103.94</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>167.85</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BARRAGAN PUENTE NATALY CAROLINA</t>
+          <t>BECERRA FARIAS ROSA DAYANA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="5">
@@ -2589,11 +2589,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BECERRA FARIAS ROSA DAYANA</t>
+          <t>BELTRAN ESPINOZA SONIA SARITA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>1856.61</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6">
@@ -2616,14 +2616,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BELTRAN ESPINOZA SONIA SARITA</t>
+          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1856.61</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1843.17</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BRAZALES BASTIDAS MERCY JANETH</t>
+          <t>CERAMICAS AL COSTO S.A.S.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -2653,13 +2653,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>154.22</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
@@ -2670,14 +2670,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
+          <t>CERAMICCENTER CIA. LTDA.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1843.17</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2697,11 +2697,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CENYCA S.C.C.</t>
+          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>2544.36</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
@@ -2724,23 +2724,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CERAMICAS AL COSTO S.A.S.</t>
+          <t>CONZA VEGA FRANCO BLADYMIR</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>396.6</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>154.22</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="11">
@@ -2751,23 +2751,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CERAMICCENTER CIA. LTDA.</t>
+          <t>CULMA OVIEDO NINI JOHANA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>4575.84</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>1614.42</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="12">
@@ -2778,11 +2778,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHUQUIZAN MUESES MARIA ROSARIO</t>
+          <t>DDH S.A.S.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>396.58</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
@@ -2805,23 +2805,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
+          <t>F.V - AREA ANDINA S.A.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2544.36</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>5382.95</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>976.35</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="14">
@@ -2832,11 +2832,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CONZA VEGA FRANCO BLADYMIR</t>
+          <t>FERRIACABADOS MACONSE</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>396.6</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2859,23 +2859,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CORTEZ GALARZA MARIA ISABEL</t>
+          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>10399.61</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>-7097.63</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>356.4</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CULMA OVIEDO NINI JOHANA</t>
+          <t>GOMEZ VALDIVIESO CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4575.84</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1614.42</v>
+        <v>2289.43</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -2913,11 +2913,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DDH S.A.S.</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>396.58</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2940,23 +2940,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>F.V - AREA ANDINA S.A.</t>
+          <t>MALO LARREA JAVIER EDUARDO</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>2625.73</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5382.95</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>976.35</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19">
@@ -2967,23 +2967,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FERRIACABADOS MACONSE</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>6670.46</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>-1260.23</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>2052.09</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FERRONORTECORP CIA. LTDA.</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -3021,23 +3021,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
+          <t>MORALES CORTEZ KLEVER VINICIO</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>10399.61</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-7097.63</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>356.4</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GOMEZ VALDIVIESO CARLOS EDUARDO</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -3058,13 +3058,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2289.43</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MACAS ROMERO HERNAN TULIO</t>
+          <t>NIZA ARIAS YOSELIN EDITH</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -3129,11 +3129,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MALO LARREA JAVIER EDUARDO</t>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2625.73</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3156,17 +3156,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6670.46</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-1260.23</v>
+        <v>131.05</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2052.09</v>
+        <v>1183.89</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
@@ -3183,14 +3183,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0</v>
+        <v>11174.98</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>110.19</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="28">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MORALES CORTEZ KLEVER VINICIO</t>
+          <t>VARIEDADES-PAS SAS</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -3220,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>294.49</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>9544.01</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3291,390 +3291,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NIZA ARIAS YOSELIN EDITH</t>
+          <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0</v>
+        <v>18379.73</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>55908.46</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NOGALES DOTA ALEX DAVID</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>PUCHAICELA AGUINZACA JENNY GEOVANNA</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>SAAVEDRA &amp; SANTANDER CIA.</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SOCIEDAD CIVIL COMERCIAL FERRETERIA MACONSE</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>131.05</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>1183.89</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>11174.98</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>110.19</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>VARIEDADES-PAS SAS</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>294.49</v>
-      </c>
-      <c r="F39" s="2" t="n">
+      <c r="C32" s="6" t="n">
+        <v>59020.5</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-786.5600000000002</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>64997.6</v>
+      </c>
+      <c r="F32" s="6" t="n">
         <v>9544.01</v>
       </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>VILLEGAS BAYAS NANCY CECILIA</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>18379.73</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>55908.46</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" s="6" t="n">
-        <v>59020.5</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>-786.5600000000002</v>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>64997.6</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>9544.01</v>
-      </c>
-      <c r="G45" s="6" t="n">
+      <c r="G32" s="6" t="n">
         <v>41650</v>
       </c>
     </row>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1364.92</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>932.77</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>22.74</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>3425.52</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>515.26</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
@@ -2366,52 +2366,52 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>1 de 30</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>4 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>2297.69</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>22.74</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>500</v>
@@ -2872,7 +2872,7 @@
         <v>356.4</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>3425.52</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>2000</v>
@@ -3169,7 +3169,7 @@
         <v>1183.89</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>515.26</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1500</v>
@@ -3196,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>8000</v>
@@ -3321,7 +3321,7 @@
         <v>64997.6</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>9544.01</v>
+        <v>16388.22</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3344,7 +3344,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3420,13 +3420,13 @@
         <v>2450</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1364.92</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2450</v>
+        <v>1085.08</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>0.5571102040816327</v>
       </c>
     </row>
     <row r="4">
@@ -3468,13 +3468,13 @@
         <v>133.5</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>133.5</v>
+        <v>-449.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>4.367041198501872</v>
       </c>
     </row>
     <row r="6">
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>932.77</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>-932.77</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3612,13 +3612,13 @@
         <v>38234</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8339.67</v>
+        <v>12303.19</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>29894.33</v>
+        <v>25930.81</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.2181218287388189</v>
+        <v>0.321786629701313</v>
       </c>
     </row>
     <row r="12">
@@ -3655,13 +3655,13 @@
         <v>43267.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9544.01</v>
+        <v>16388.22</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>33723.49</v>
+        <v>26879.28</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.2205814988155082</v>
+        <v>0.3787651239382909</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2899,7 +2899,7 @@
         <v>2289.43</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>189.57</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3000</v>
@@ -3321,7 +3321,7 @@
         <v>64997.6</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>16388.22</v>
+        <v>16577.79</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3345,7 +3345,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3588,13 +3588,13 @@
         <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>189.57</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>220</v>
+        <v>30.43000000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.8616818181818181</v>
       </c>
     </row>
     <row r="11">
@@ -3655,13 +3655,13 @@
         <v>43267.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>16388.22</v>
+        <v>16577.79</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26879.28</v>
+        <v>26689.71</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3787651239382909</v>
+        <v>0.3831464725255677</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1364.92</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>932.77</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>22.74</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3425.52</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>515.26</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>289.94</v>
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0</v>
@@ -2100,10 +2100,10 @@
         <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8339.67</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>914.4</v>
+        <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2406,17 +2406,17 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>4 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2458,8 +2458,8 @@
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2476,22 +2476,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>103.94</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>103.94</v>
+        <v>167.85</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>167.85</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1856.61</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>1843.17</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1843.17</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -2650,10 +2650,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>154.22</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>154.22</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -2701,16 +2701,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2544.36</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>2297.69</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2297.69</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>396.6</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4575.84</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1614.42</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1614.42</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>396.58</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>22.74</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>22.74</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>500</v>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>5382.95</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5382.95</v>
+        <v>976.35</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>976.35</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2863,16 +2863,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10399.61</v>
+        <v>-7097.63</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-7097.63</v>
+        <v>356.4</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>356.4</v>
+        <v>3425.52</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>3425.52</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>2000</v>
@@ -2893,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>2289.43</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2289.43</v>
+        <v>189.57</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>189.57</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3000</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2625.73</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6670.46</v>
+        <v>-1260.23</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-1260.23</v>
+        <v>2052.09</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2052.09</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
@@ -3160,16 +3160,16 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>131.05</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>131.05</v>
+        <v>1183.89</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1183.89</v>
+        <v>515.26</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>515.26</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1500</v>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>11174.98</v>
+        <v>110.19</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>110.19</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>8000</v>
@@ -3217,13 +3217,13 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>294.49</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>294.49</v>
+        <v>9544.01</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>9544.01</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
@@ -3295,13 +3295,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>18379.73</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0</v>
+        <v>55908.46</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>55908.46</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -3312,16 +3312,16 @@
     </row>
     <row r="32">
       <c r="C32" s="6" t="n">
-        <v>59020.5</v>
+        <v>-786.5600000000002</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-786.5600000000002</v>
+        <v>64997.6</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>64997.6</v>
+        <v>16577.79</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>16577.79</v>
+        <v>0</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -3338,15 +3338,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3393,13 +3393,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>500</v>
+        <v>136.08</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>500</v>
+        <v>136.08</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2450</v>
+        <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1364.92</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1085.08</v>
+        <v>3800</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5571102040816327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>198</v>
+        <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>198</v>
+        <v>199.5</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -3465,16 +3465,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>133.5</v>
+        <v>172.82</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-449.5</v>
+        <v>172.82</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4.367041198501872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3489,16 +3489,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>312</v>
+        <v>263.55</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>289.94</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>22.06</v>
+        <v>263.55</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.9292948717948718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>932.77</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-932.77</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3561,13 +3561,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>400</v>
+        <v>203.763</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>400</v>
+        <v>203.763</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3585,16 +3585,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>189.57</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>30.43000000000001</v>
+        <v>115</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8616818181818181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3605,20 +3605,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>38234</v>
+        <v>254</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12303.19</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25930.81</v>
+        <v>254</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.321786629701313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3629,39 +3629,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>29057</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>29057</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>570</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>914.4</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>-344.4</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>1.60421052631579</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>43267.5</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>16577.79</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>26689.71</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.3831464725255677</v>
+      <c r="C14" s="2" t="n">
+        <v>34779.313</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>34779.313</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1219.72</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>0 de 30</t>
+          <t>1 de 30</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>1219.72</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>3000</v>
@@ -3321,7 +3321,7 @@
         <v>16577.79</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0</v>
+        <v>1219.72</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3344,9 +3344,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3612,13 +3612,13 @@
         <v>254</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1219.72</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>254</v>
+        <v>-965.72</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>4.802047244094489</v>
       </c>
     </row>
     <row r="12">
@@ -3679,13 +3679,13 @@
         <v>34779.313</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>1219.72</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>34779.313</v>
+        <v>33559.593</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>0.03507027295220006</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2299,144 +2299,84 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ZAMBRANO ZAMBRANO JOSE ALEJANDRO</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>1 de 30</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="R32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
         </is>
       </c>
     </row>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>-16.52</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>3425.52</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>-16.52</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>2000</v>
@@ -3261,7 +3261,7 @@
         <v>16577.79</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1219.72</v>
+        <v>1203.2</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3286,7 +3286,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3576,13 +3576,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>-16.52</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>29057</v>
+        <v>29073.52</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005685377017586124</v>
       </c>
     </row>
     <row r="13">
@@ -3619,13 +3619,13 @@
         <v>34779.313</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1219.72</v>
+        <v>1203.2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>33559.593</v>
+        <v>33576.113</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.03507027295220006</v>
+        <v>0.03459527794582946</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1462.41</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1219.72</v>
+        <v>3397.8</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>0</v>
+        <v>453.18</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>987.15</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>644.64</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>6266.67</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>13307.98</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2306,67 +2306,67 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
+          <t>3 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>2 de 29</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>1 de 29</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2650,7 +2650,7 @@
         <v>2297.69</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>1462.41</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1219.72</v>
+        <v>3850.98</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>3000</v>
@@ -2839,7 +2839,7 @@
         <v>189.57</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>1830.03</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3000</v>
@@ -3001,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>19574.65</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>16577.79</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1203.2</v>
+        <v>26701.55</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3285,8 +3285,8 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3360,13 +3360,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>8716.23</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3800</v>
+        <v>-4916.23</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>2.293744736842105</v>
       </c>
     </row>
     <row r="4">
@@ -3456,13 +3456,13 @@
         <v>250</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>453.18</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>250</v>
+        <v>-203.18</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1.81272</v>
       </c>
     </row>
     <row r="8">
@@ -3528,13 +3528,13 @@
         <v>115</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>198.24</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>115</v>
+        <v>-83.24000000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.723826086956522</v>
       </c>
     </row>
     <row r="11">
@@ -3552,13 +3552,13 @@
         <v>254</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1219.72</v>
+        <v>3397.8</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-965.72</v>
+        <v>-3143.8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4.802047244094489</v>
+        <v>13.37716535433071</v>
       </c>
     </row>
     <row r="12">
@@ -3576,13 +3576,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-16.52</v>
+        <v>13936.1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>29073.52</v>
+        <v>15120.9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.0005685377017586124</v>
+        <v>0.479612485803765</v>
       </c>
     </row>
     <row r="13">
@@ -3619,13 +3619,13 @@
         <v>34779.313</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1203.2</v>
+        <v>26701.55</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>33576.113</v>
+        <v>8077.763</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.03459527794582946</v>
+        <v>0.7677423070432703</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>1882.63</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
+        <v>738.77</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>4 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>1882.63</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>1500</v>
@@ -3136,7 +3136,7 @@
         <v>583</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>738.77</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>8000</v>
@@ -3261,7 +3261,7 @@
         <v>16577.79</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>26701.55</v>
+        <v>29322.95</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3286,7 +3286,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3576,13 +3576,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>13936.1</v>
+        <v>16557.5</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15120.9</v>
+        <v>12499.5</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.479612485803765</v>
+        <v>0.5698282685755583</v>
       </c>
     </row>
     <row r="13">
@@ -3619,13 +3619,13 @@
         <v>34779.313</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>26701.55</v>
+        <v>29322.95</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8077.763</v>
+        <v>5456.363</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7677423070432703</v>
+        <v>0.8431146986715925</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>5291.95</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>4 de 29</t>
+          <t>5 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>5291.95</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>8000</v>
@@ -3261,7 +3261,7 @@
         <v>16577.79</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>29322.95</v>
+        <v>34614.9</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3284,7 +3284,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3576,13 +3576,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>16557.5</v>
+        <v>21849.45</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12499.5</v>
+        <v>7207.549999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5698282685755583</v>
+        <v>0.7519513370272224</v>
       </c>
     </row>
     <row r="13">
@@ -3619,13 +3619,13 @@
         <v>34779.313</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>29322.95</v>
+        <v>34614.9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5456.363</v>
+        <v>164.4129999999992</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8431146986715925</v>
+        <v>0.9952726783303626</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5291.95</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1462.41</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3397.8</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>453.18</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>-16.52</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>987.15</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>644.64</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1882.63</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6266.67</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13307.98</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>738.77</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>5 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
@@ -2397,9 +2397,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2416,22 +2416,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>103.94</v>
+        <v>167.85</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>167.85</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>5291.95</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5291.95</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>8000</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1843.17</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>154.22</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>154.22</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>2297.69</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2297.69</v>
+        <v>1462.41</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1462.41</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>1614.42</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1614.42</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>3850.98</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3850.98</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>3000</v>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>22.74</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>22.74</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5382.95</v>
+        <v>976.35</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>976.35</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -2803,16 +2803,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-7097.63</v>
+        <v>356.4</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>356.4</v>
+        <v>3425.52</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3425.52</v>
+        <v>-16.52</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-16.52</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>2000</v>
@@ -2830,16 +2830,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>2289.43</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2289.43</v>
+        <v>189.57</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>189.57</v>
+        <v>1830.03</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1830.03</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3000</v>
@@ -2890,10 +2890,10 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>1882.63</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1882.63</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>1500</v>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-1260.23</v>
+        <v>2052.09</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2052.09</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -2998,10 +2998,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>19574.65</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>19574.65</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3100,13 +3100,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>131.05</v>
+        <v>1183.89</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1183.89</v>
+        <v>515.26</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>515.26</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
@@ -3127,16 +3127,16 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>110.19</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>583</v>
+        <v>738.77</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>738.77</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>8000</v>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0</v>
+        <v>294.49</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>294.49</v>
+        <v>9544.01</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9544.01</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0</v>
+        <v>55908.46</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>55908.46</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0</v>
@@ -3252,16 +3252,16 @@
     </row>
     <row r="32">
       <c r="C32" s="6" t="n">
-        <v>-786.5600000000002</v>
+        <v>64997.6</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>64997.6</v>
+        <v>16577.79</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>16577.79</v>
+        <v>34614.9</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>34614.9</v>
+        <v>0</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>67.44</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>67.44</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>500</v>
@@ -3261,7 +3261,7 @@
         <v>34614.9</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0</v>
+        <v>67.44</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -3278,15 +3278,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3360,13 +3360,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8716.23</v>
+        <v>67.44</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-4916.23</v>
+        <v>3732.56</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.293744736842105</v>
+        <v>0.01774736842105263</v>
       </c>
     </row>
     <row r="4">
@@ -3405,13 +3405,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>172.82</v>
+        <v>198.5</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>172.82</v>
+        <v>198.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3425,17 +3425,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>INODOROS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>263.55</v>
+        <v>655</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>263.55</v>
+        <v>655</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -3449,20 +3449,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>250</v>
+        <v>463</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>453.18</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-203.18</v>
+        <v>463</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.81272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3473,17 +3473,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3497,17 +3497,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>203.763</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>203.763</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3521,20 +3521,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>115</v>
+        <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>198.24</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-83.24000000000001</v>
+        <v>203.763</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.723826086956522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3545,20 +3545,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>254</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3397.8</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-3143.8</v>
+        <v>115</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>13.37716535433071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3569,20 +3569,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>29057</v>
+        <v>960</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>21849.45</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7207.549999999999</v>
+        <v>960</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.7519513370272224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3593,39 +3593,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>35057</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>35057</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>327.6</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>327.6</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>34779.313</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>34614.9</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>164.4129999999992</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.9952726783303626</v>
+      <c r="C15" s="2" t="n">
+        <v>42365.443</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>67.44</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>42298.003</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.001591863443986647</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>-633.71</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3001,7 +3001,7 @@
         <v>19574.65</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>-633.71</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>34614.9</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>67.44</v>
+        <v>-566.27</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3284,7 +3284,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3360,13 +3360,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>67.44</v>
+        <v>-566.27</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3732.56</v>
+        <v>4366.27</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.01774736842105263</v>
+        <v>-0.1490184210526316</v>
       </c>
     </row>
     <row r="4">
@@ -3643,13 +3643,13 @@
         <v>42365.443</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>67.44</v>
+        <v>-566.27</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>42298.003</v>
+        <v>42931.713</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.001591863443986647</v>
+        <v>-0.01336631839303557</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>169.3</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -3136,7 +3136,7 @@
         <v>738.77</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>169.3</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>8000</v>
@@ -3261,7 +3261,7 @@
         <v>34614.9</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-566.27</v>
+        <v>-396.97</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3576,13 +3576,13 @@
         <v>960</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>169.3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>960</v>
+        <v>790.7</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.1763541666666667</v>
       </c>
     </row>
     <row r="13">
@@ -3643,13 +3643,13 @@
         <v>42365.443</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-566.27</v>
+        <v>-396.97</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>42931.713</v>
+        <v>42762.413</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01336631839303557</v>
+        <v>-0.009370136882553075</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>71.11</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>71.11</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1500</v>
@@ -3261,7 +3261,7 @@
         <v>34614.9</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-396.97</v>
+        <v>-325.86</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>41650</v>
@@ -3286,7 +3286,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3600,13 +3600,13 @@
         <v>35057</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>71.11</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>35057</v>
+        <v>34985.89</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.002028410873719942</v>
       </c>
     </row>
     <row r="14">
@@ -3643,13 +3643,13 @@
         <v>42365.443</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-396.97</v>
+        <v>-325.86</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>42762.413</v>
+        <v>42691.303</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.009370136882553075</v>
+        <v>-0.007691646231576051</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>LOACHAMIN TOPON FERNANDO HERNAN</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>3336.4</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MALO LARREA JAVIER EDUARDO</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>MALO LARREA JAVIER EDUARDO</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,14 +1706,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-633.71</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -1766,14 +1766,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>-633.71</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NIZA ARIAS YOSELIN EDITH</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>NIZA ARIAS YOSELIN EDITH</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>169.3</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VARIEDADES-PAS SAS</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>169.3</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>0</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>VARIEDADES-PAS SAS</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2246,137 +2246,197 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>1 de 29</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>1 de 29</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>1 de 29</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="R31" s="4" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>2 de 30</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2853,7 +2913,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>LOACHAMIN TOPON FERNANDO HERNAN</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2866,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>3336.4</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2880,7 +2940,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MALO LARREA JAVIER EDUARDO</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -2890,13 +2950,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1882.63</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2907,17 +2967,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>MALO LARREA JAVIER EDUARDO</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2052.09</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>1882.63</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
@@ -2934,11 +2994,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>2052.09</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
@@ -2950,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="21">
@@ -2961,7 +3021,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MORALES CORTEZ KLEVER VINICIO</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -2988,7 +3048,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>MORALES CORTEZ KLEVER VINICIO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -2998,10 +3058,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>19574.65</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-633.71</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3015,7 +3075,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -3025,10 +3085,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>19574.65</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>-633.71</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3042,7 +3102,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NIZA ARIAS YOSELIN EDITH</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -3069,7 +3129,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>NIZA ARIAS YOSELIN EDITH</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -3096,14 +3156,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1183.89</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>515.26</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
@@ -3112,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3123,23 +3183,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0</v>
+        <v>1183.89</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>583</v>
+        <v>515.26</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>738.77</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>169.3</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>8000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="28">
@@ -3150,23 +3210,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VARIEDADES-PAS SAS</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>294.49</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9544.01</v>
+        <v>583</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>738.77</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>169.3</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="29">
@@ -3177,14 +3237,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
+          <t>VARIEDADES-PAS SAS</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0</v>
+        <v>294.49</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0</v>
+        <v>9544.01</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
@@ -3204,7 +3264,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3231,39 +3291,66 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C32" s="2" t="n">
         <v>55908.46</v>
       </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="32">
-      <c r="C32" s="6" t="n">
+    <row r="33">
+      <c r="C33" s="6" t="n">
         <v>64997.6</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D33" s="6" t="n">
         <v>16577.79</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E33" s="6" t="n">
         <v>34614.9</v>
       </c>
-      <c r="F32" s="6" t="n">
-        <v>-325.86</v>
-      </c>
-      <c r="G32" s="6" t="n">
+      <c r="F33" s="6" t="n">
+        <v>3010.54</v>
+      </c>
+      <c r="G33" s="6" t="n">
         <v>41650</v>
       </c>
     </row>
@@ -3286,7 +3373,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3600,13 +3687,13 @@
         <v>35057</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>71.11</v>
+        <v>3407.51</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>34985.89</v>
+        <v>31649.49</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.002028410873719942</v>
+        <v>0.09719913284080213</v>
       </c>
     </row>
     <row r="14">
@@ -3643,13 +3730,13 @@
         <v>42365.443</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-325.86</v>
+        <v>3010.54</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>42691.303</v>
+        <v>39354.903</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.007691646231576051</v>
+        <v>0.07106121845580608</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>54.72</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>2 de 30</t>
+          <t>3 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2980,7 +2980,7 @@
         <v>1882.63</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>54.72</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>1500</v>
@@ -3348,7 +3348,7 @@
         <v>34614.9</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>3010.54</v>
+        <v>3065.26</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>41650</v>
@@ -3687,13 +3687,13 @@
         <v>35057</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3407.51</v>
+        <v>3462.23</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>31649.49</v>
+        <v>31594.77</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.09719913284080213</v>
+        <v>0.09876001939698206</v>
       </c>
     </row>
     <row r="14">
@@ -3730,13 +3730,13 @@
         <v>42365.443</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3010.54</v>
+        <v>3065.26</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>39354.903</v>
+        <v>39300.183</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.07106121845580608</v>
+        <v>0.07235283719327566</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -3365,7 +3365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3512,17 +3512,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INODOROS</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>655</v>
+        <v>463</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>655</v>
+        <v>463</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>463</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>463</v>
+        <v>250</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -3560,17 +3560,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>203.763</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>203.763</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3608,17 +3608,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>203.763</v>
+        <v>115</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>203.763</v>
+        <v>115</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -3632,20 +3632,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>115</v>
+        <v>960</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>169.3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115</v>
+        <v>790.7</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.1763541666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3656,20 +3656,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>960</v>
+        <v>35057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>169.3</v>
+        <v>3462.23</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>790.7</v>
+        <v>31594.77</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1763541666666667</v>
+        <v>0.09876001939698206</v>
       </c>
     </row>
     <row r="13">
@@ -3680,63 +3680,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>35057</v>
+        <v>327.6</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3462.23</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>31594.77</v>
+        <v>327.6</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.09876001939698206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>327.6</v>
+        <v>41710.443</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>3065.26</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>327.6</v>
+        <v>38645.183</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>42365.443</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>3065.26</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>39300.183</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.07235283719327566</v>
+        <v>0.07348903007335597</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>3302.63</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>4927.44</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>2 de 30</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>3 de 30</t>
+          <t>4 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2710,7 +2710,7 @@
         <v>1462.41</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>3302.63</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>4927.44</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1500</v>
@@ -3348,7 +3348,7 @@
         <v>34614.9</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>3065.26</v>
+        <v>11295.33</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>41650</v>
@@ -3639,13 +3639,13 @@
         <v>960</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>169.3</v>
+        <v>3471.93</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>790.7</v>
+        <v>-2511.93</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1763541666666667</v>
+        <v>3.61659375</v>
       </c>
     </row>
     <row r="12">
@@ -3663,13 +3663,13 @@
         <v>35057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3462.23</v>
+        <v>8389.67</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>31594.77</v>
+        <v>26667.33</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.09876001939698206</v>
+        <v>0.2393151153835183</v>
       </c>
     </row>
     <row r="13">
@@ -3706,13 +3706,13 @@
         <v>41710.443</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3065.26</v>
+        <v>11295.33</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>38645.183</v>
+        <v>30415.113</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.07348903007335597</v>
+        <v>0.2708034052767073</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>67.44</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>71.11</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>3302.63</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3336.4</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>54.72</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4927.44</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-633.71</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>169.3</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>4 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2456,10 +2456,10 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2476,22 +2476,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>167.85</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -2569,10 +2569,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>5291.95</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5291.95</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -2599,10 +2599,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>67.44</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67.44</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>500</v>
@@ -2647,16 +2647,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>154.22</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>71.11</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>71.11</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1500</v>
@@ -2701,16 +2701,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>2297.69</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2297.69</v>
+        <v>1462.41</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1462.41</v>
+        <v>3302.63</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3302.63</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1614.42</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>3850.98</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3850.98</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>22.74</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>22.74</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>976.35</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>356.4</v>
+        <v>3425.52</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3425.52</v>
+        <v>-16.52</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-16.52</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -2890,13 +2890,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2289.43</v>
+        <v>189.57</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>189.57</v>
+        <v>1830.03</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1830.03</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -2923,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>3336.4</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3336.4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2974,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1882.63</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1882.63</v>
+        <v>54.72</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>54.72</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>1500</v>
@@ -2998,16 +2998,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2052.09</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>4927.44</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4927.44</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1500</v>
@@ -3082,13 +3082,13 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>19574.65</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>19574.65</v>
+        <v>-633.71</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-633.71</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1183.89</v>
+        <v>515.26</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>515.26</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
@@ -3214,16 +3214,16 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>583</v>
+        <v>738.77</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>738.77</v>
+        <v>169.3</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>169.3</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>8000</v>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>294.49</v>
+        <v>9544.01</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>9544.01</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>55908.46</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
@@ -3339,16 +3339,16 @@
     </row>
     <row r="33">
       <c r="C33" s="6" t="n">
-        <v>64997.6</v>
+        <v>16577.79</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>16577.79</v>
+        <v>34614.9</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>34614.9</v>
+        <v>11295.33</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>11295.33</v>
+        <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>41650</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="16">
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17">
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="18">
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19">
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="22">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28">
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="29">
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30">
@@ -3334,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="33">
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>41650</v>
+        <v>38500</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2451,7 +2451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2535,14 +2535,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BARRAGAN PUENTE NATALY CAROLINA</t>
+          <t>BECERRA FARIAS ROSA DAYANA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>5291.95</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -2562,23 +2562,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BECERRA FARIAS ROSA DAYANA</t>
+          <t>BELTRAN ESPINOZA SONIA SARITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5291.95</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>67.44</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BELTRAN ESPINOZA SONIA SARITA</t>
+          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -2599,13 +2599,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>67.44</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CAIZA COLLAGUAZO ROCIO PILAR</t>
+          <t>CERAMICAS AL COSTO S.A.S.</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -2626,13 +2626,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>71.11</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CERAMICAS AL COSTO S.A.S.</t>
+          <t>CERAMICCENTER CIA. LTDA.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -2653,13 +2653,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>71.11</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CERAMICCENTER CIA. LTDA.</t>
+          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>2297.69</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>1462.41</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>3302.63</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONSTANTE CAMACHO ARIANA ELIZABETH</t>
+          <t>CONZA VEGA FRANCO BLADYMIR</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2297.69</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1462.41</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3302.63</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="10">
@@ -2724,14 +2724,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CONZA VEGA FRANCO BLADYMIR</t>
+          <t>CULMA OVIEDO NINI JOHANA</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>3850.98</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CULMA OVIEDO NINI JOHANA</t>
+          <t>DDH S.A.S.</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>22.74</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3850.98</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2778,11 +2778,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DDH S.A.S.</t>
+          <t>F.V - AREA ANDINA S.A.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>22.74</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="13">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F.V - AREA ANDINA S.A.</t>
+          <t>FERRIACABADOS MACONSE</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2832,14 +2832,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FERRIACABADOS MACONSE</t>
+          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>3425.52</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>-16.52</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="15">
@@ -2859,14 +2859,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
+          <t>GOMEZ VALDIVIESO CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3425.52</v>
+        <v>189.57</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-16.52</v>
+        <v>1830.03</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
@@ -2886,23 +2886,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GOMEZ VALDIVIESO CARLOS EDUARDO</t>
+          <t>LOACHAMIN TOPON FERNANDO HERNAN</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>189.57</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1830.03</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>3336.4</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="17">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LOACHAMIN TOPON FERNANDO HERNAN</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2923,13 +2923,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3336.4</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
@@ -2940,23 +2940,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>MALO LARREA JAVIER EDUARDO</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>1882.63</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>54.72</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19">
@@ -2967,23 +2967,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MALO LARREA JAVIER EDUARDO</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1882.63</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>54.72</v>
+        <v>4927.44</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -3004,13 +3004,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4927.44</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="21">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>MORALES CORTEZ KLEVER VINICIO</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3048,17 +3048,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MORALES CORTEZ KLEVER VINICIO</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>19574.65</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>-633.71</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -3075,17 +3075,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>19574.65</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-633.71</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>NIZA ARIAS YOSELIN EDITH</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -3129,11 +3129,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NIZA ARIAS YOSELIN EDITH</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0</v>
+        <v>515.26</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26">
@@ -3156,23 +3156,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>738.77</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>169.3</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="27">
@@ -3183,11 +3183,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>VARIEDADES-PAS SAS</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>515.26</v>
+        <v>9544.01</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
@@ -3210,147 +3210,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>738.77</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>169.3</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>VARIEDADES-PAS SAS</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>9544.01</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>VELASCO SAMANIEGO JIMMY FABRICIO</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" s="6" t="n">
+      <c r="C29" s="6" t="n">
         <v>16577.79</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D29" s="6" t="n">
         <v>34614.9</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E29" s="6" t="n">
         <v>11295.33</v>
       </c>
-      <c r="F33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6" t="n">
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="n">
         <v>38500</v>
       </c>
     </row>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -3257,15 +3257,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3339,13 +3339,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-566.27</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4366.27</v>
+        <v>3800</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.1490184210526316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FREGADEROS DE COCINA</t>
+          <t>CERAMICA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>199.5</v>
+        <v>3973</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>199.5</v>
+        <v>3973</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -3380,17 +3380,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GRIFERIAS</t>
+          <t>FREGADEROS DE COCINA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>198.5</v>
+        <v>199.5</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>198.5</v>
+        <v>199.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3404,17 +3404,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>GRIFERIAS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>463</v>
+        <v>198.5</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>463</v>
+        <v>198.5</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -3428,17 +3428,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>INODOROS</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>250</v>
+        <v>655</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>250</v>
+        <v>655</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -3452,17 +3452,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3476,17 +3476,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>203.763</v>
+        <v>250</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>203.763</v>
+        <v>250</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -3500,17 +3500,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -3524,20 +3524,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>960</v>
+        <v>203.763</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3471.93</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-2511.93</v>
+        <v>203.763</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.61659375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3548,20 +3548,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>35057</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8389.67</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>26667.33</v>
+        <v>115</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.2393151153835183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3572,39 +3572,87 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>PIEDRA SINTERIZADA</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>960</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>960</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>39283</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>39283</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>327.6</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>327.6</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>41710.443</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>11295.33</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>30415.113</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.2708034052767073</v>
+      <c r="C16" s="2" t="n">
+        <v>50564.443</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>50564.443</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>-71.11</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2629,7 +2629,7 @@
         <v>71.11</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>-71.11</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>500</v>
@@ -3240,7 +3240,7 @@
         <v>11295.33</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0</v>
+        <v>-71.11</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3263,9 +3263,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3603,13 +3603,13 @@
         <v>39283</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>-71.11</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>39283</v>
+        <v>39354.11</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>-0.001810197795484052</v>
       </c>
     </row>
     <row r="15">
@@ -3646,13 +3646,13 @@
         <v>50564.443</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>-71.11</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50564.443</v>
+        <v>50635.553</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0</v>
+        <v>-0.001406324202958193</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F.V - AREA ANDINA S.A.</t>
+          <t>DIAZ CUSICAGUA XIMENA ELIZABETH</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>327.77</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>0</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FERRIACABADOS MACONSE</t>
+          <t>F.V - AREA ANDINA S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
+          <t>FERRIACABADOS MACONSE</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GOMEZ VALDIVIESO CARLOS EDUARDO</t>
+          <t>GANCHOZO CEDEÑO YURI MERCEDES</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LOACHAMIN TOPON FERNANDO HERNAN</t>
+          <t>GOMEZ VALDIVIESO CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
+          <t>LOACHAMIN TOPON FERNANDO HERNAN</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MALO LARREA JAVIER EDUARDO</t>
+          <t>LUNA PAZMIÑO MYRIAM DEL ROCIO</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MAÑAY REAL NOEMI ELIZABETH</t>
+          <t>MALO LARREA JAVIER EDUARDO</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
+          <t>MAÑAY REAL NOEMI ELIZABETH</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MUNDIACABADOS CIA. LTDA.</t>
+          <t>MERIZALDE PEREIRA KAREN ELIZABETH</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MUNDO-CERAMICO CIA.LTDA.</t>
+          <t>MUNDIACABADOS CIA. LTDA.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NIZA ARIAS YOSELIN EDITH</t>
+          <t>MUNDO-CERAMICO CIA.LTDA.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>NIZA ARIAS YOSELIN EDITH</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VARIEDADES-PAS SAS</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>VARIEDADES-PAS SAS</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2306,137 +2306,197 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="R32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>1 de 31</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
         </is>
       </c>
     </row>
@@ -3579,13 +3639,13 @@
         <v>960</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>327.77</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>960</v>
+        <v>632.23</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.3414270833333333</v>
       </c>
     </row>
     <row r="14">
@@ -3646,13 +3706,13 @@
         <v>50564.443</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-71.11</v>
+        <v>256.66</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50635.553</v>
+        <v>50307.783</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.001406324202958193</v>
+        <v>0.005075898888078328</v>
       </c>
     </row>
   </sheetData>
